--- a/TUCUMAN 1061/Septiembre/tucuman Septiembre.xlsx
+++ b/TUCUMAN 1061/Septiembre/tucuman Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE51ACC-5FBB-4A67-8995-3F356FBF4CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9604F5B8-6C80-482F-A0DE-EC1712BCF21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="167">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -554,9 +554,6 @@
     <t>Luz</t>
   </si>
   <si>
-    <t>Digitalizacion de copias - Escrbania Narosky</t>
-  </si>
-  <si>
     <t xml:space="preserve">PERIODO: SEPTIEMBRE </t>
   </si>
   <si>
@@ -564,6 +561,12 @@
   </si>
   <si>
     <t>Administraciòn SEPTIEMBRE 2025:</t>
+  </si>
+  <si>
+    <t>Digitalizacion acta - Escribania Narosky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adelanto Sr. Leo trabajo en medianera </t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1364,7 @@
     <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1802,14 +1805,6 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="22" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="35" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="35" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2208,15 +2203,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2226,7 +2221,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="D2" s="13" t="s">
         <v>0</v>
@@ -2236,7 +2231,7 @@
       </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
@@ -2247,7 +2242,7 @@
       <c r="F3" s="194"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="D4" s="13" t="s">
         <v>2</v>
@@ -2257,18 +2252,18 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="D5" s="42" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
@@ -2276,13 +2271,13 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2292,11 +2287,11 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
@@ -2305,7 +2300,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2315,7 +2310,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="204" t="s">
         <v>11</v>
       </c>
@@ -2327,7 +2322,7 @@
       <c r="G12" s="204"/>
       <c r="H12" s="204"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -2337,7 +2332,7 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>60</v>
       </c>
@@ -2350,13 +2345,13 @@
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
       <c r="H14" s="189">
-        <f>373590.5+373591*5%</f>
-        <v>392270.05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <f>392270+392270*2%</f>
+        <v>400115.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -2364,11 +2359,11 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="245">
+      <c r="H15" s="189">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
         <v>5</v>
       </c>
@@ -2380,10 +2375,10 @@
       <c r="G16" s="22"/>
       <c r="H16" s="181">
         <f>SUM(H13:H15)</f>
-        <v>396300.33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>404145.68000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
@@ -2393,7 +2388,7 @@
       <c r="G17" s="24"/>
       <c r="H17" s="43"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="205" t="s">
         <v>6</v>
       </c>
@@ -2405,7 +2400,7 @@
       <c r="G18" s="206"/>
       <c r="H18" s="207"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>59</v>
       </c>
@@ -2415,11 +2410,11 @@
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="240">
+      <c r="H19" s="26">
         <v>364854.17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>58</v>
       </c>
@@ -2429,11 +2424,11 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="240">
+      <c r="H20" s="26">
         <v>533528.86</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
@@ -2448,7 +2443,7 @@
         <v>898383.03</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="208" t="s">
         <v>61</v>
       </c>
@@ -2461,7 +2456,7 @@
       <c r="H22" s="208"/>
       <c r="J22" s="26"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
         <v>142</v>
       </c>
@@ -2471,187 +2466,187 @@
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="240">
+      <c r="H23" s="26">
         <v>46638</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="241"/>
-      <c r="B24" s="242"/>
-      <c r="C24" s="243"/>
-      <c r="D24" s="242"/>
-      <c r="E24" s="242"/>
-      <c r="F24" s="242"/>
-      <c r="G24" s="242"/>
-      <c r="H24" s="244">
-        <v>400000</v>
-      </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="98" t="s">
+    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="240">
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="26">
         <v>75000</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="27">
-        <f>SUM(H23:H25)</f>
-        <v>521638</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="205" t="s">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="27">
+        <f>SUM(H23:H24)</f>
+        <v>121638</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="205" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="206"/>
-      <c r="C27" s="206"/>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="206"/>
-      <c r="G27" s="206"/>
-      <c r="H27" s="207"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
+      <c r="B26" s="206"/>
+      <c r="C26" s="206"/>
+      <c r="D26" s="206"/>
+      <c r="E26" s="206"/>
+      <c r="F26" s="206"/>
+      <c r="G26" s="206"/>
+      <c r="H26" s="207"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19" t="s">
+      <c r="B27" s="19"/>
+      <c r="C27" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="28"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="44"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="190">
+        <v>66600</v>
+      </c>
       <c r="I28" s="44"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
+      <c r="N28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="29"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="205" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="206"/>
+      <c r="C30" s="206"/>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="206"/>
+      <c r="G30" s="206"/>
+      <c r="H30" s="207"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="50"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="52"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32">
+        <f>H16+H21+H25+H28+H31</f>
+        <v>1490766.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
+    </row>
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="195" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="196"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
+      <c r="E34" s="196"/>
+      <c r="F34" s="196"/>
+      <c r="G34" s="196"/>
+      <c r="H34" s="197"/>
+      <c r="I34" s="167"/>
+      <c r="K34" s="167"/>
+    </row>
+    <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="198"/>
+      <c r="B35" s="199"/>
+      <c r="C35" s="199"/>
+      <c r="D35" s="199"/>
+      <c r="E35" s="199"/>
+      <c r="F35" s="199"/>
+      <c r="G35" s="199"/>
+      <c r="H35" s="200"/>
+    </row>
+    <row r="36" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="209" t="s">
         <v>165</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="190">
-        <v>66600</v>
-      </c>
-      <c r="I29" s="44"/>
-      <c r="N29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="29"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="205" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="206"/>
-      <c r="C31" s="206"/>
-      <c r="D31" s="206"/>
-      <c r="E31" s="206"/>
-      <c r="F31" s="206"/>
-      <c r="G31" s="206"/>
-      <c r="H31" s="207"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="52"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32">
-        <f>H16+H21+H26+H29+H32</f>
-        <v>1882921.36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A34" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="48"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="195" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="196"/>
-      <c r="C35" s="196"/>
-      <c r="D35" s="196"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="197"/>
-      <c r="I35" s="167"/>
-      <c r="K35" s="167"/>
-    </row>
-    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="198"/>
-      <c r="B36" s="199"/>
-      <c r="C36" s="199"/>
-      <c r="D36" s="199"/>
-      <c r="E36" s="199"/>
-      <c r="F36" s="199"/>
-      <c r="G36" s="199"/>
-      <c r="H36" s="200"/>
-    </row>
-    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="210"/>
+      <c r="C36" s="210"/>
+      <c r="D36" s="210"/>
+      <c r="E36" s="210"/>
+      <c r="F36" s="210"/>
+      <c r="G36" s="211"/>
+      <c r="H36" s="191">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="209" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B37" s="210"/>
       <c r="C37" s="210"/>
@@ -2660,138 +2655,143 @@
       <c r="F37" s="210"/>
       <c r="G37" s="211"/>
       <c r="H37" s="191">
-        <v>110800</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="209"/>
-      <c r="B38" s="210"/>
-      <c r="C38" s="210"/>
-      <c r="D38" s="210"/>
-      <c r="E38" s="210"/>
-      <c r="F38" s="210"/>
-      <c r="G38" s="211"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="212"/>
+      <c r="B38" s="213"/>
+      <c r="C38" s="213"/>
+      <c r="D38" s="213"/>
+      <c r="E38" s="213"/>
+      <c r="F38" s="213"/>
+      <c r="G38" s="214"/>
       <c r="H38" s="33"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="212"/>
-      <c r="B39" s="213"/>
-      <c r="C39" s="213"/>
-      <c r="D39" s="213"/>
-      <c r="E39" s="213"/>
-      <c r="F39" s="213"/>
-      <c r="G39" s="214"/>
-      <c r="H39" s="33"/>
-    </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="215" t="s">
+    <row r="39" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="216"/>
-      <c r="C40" s="216"/>
-      <c r="D40" s="216"/>
-      <c r="E40" s="216"/>
-      <c r="F40" s="216"/>
-      <c r="G40" s="217"/>
-      <c r="H40" s="34">
-        <f>SUM(H37:H39)</f>
-        <v>110800</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="187"/>
-      <c r="B41" s="187"/>
-      <c r="C41" s="187"/>
-      <c r="D41" s="187"/>
-      <c r="E41" s="187"/>
-      <c r="F41" s="187"/>
-      <c r="G41" s="187"/>
-      <c r="H41" s="188"/>
-    </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H42" s="19"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="192" t="s">
+      <c r="B39" s="216"/>
+      <c r="C39" s="216"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="216"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="217"/>
+      <c r="H39" s="34">
+        <f>SUM(H36:H38)</f>
+        <v>445500</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="187"/>
+      <c r="B40" s="187"/>
+      <c r="C40" s="187"/>
+      <c r="D40" s="187"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="187"/>
+      <c r="H40" s="188"/>
+    </row>
+    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="19"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="192" t="s">
         <v>145</v>
       </c>
-      <c r="B43" s="192"/>
-      <c r="C43" s="192"/>
-      <c r="D43" s="192"/>
-      <c r="E43" s="192"/>
-      <c r="F43" s="192"/>
-      <c r="G43" s="192"/>
-      <c r="H43" s="32">
-        <f>+H33+H34</f>
-        <v>1882921.36</v>
-      </c>
-      <c r="J43" s="167"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="30" t="s">
+      <c r="B42" s="192"/>
+      <c r="C42" s="192"/>
+      <c r="D42" s="192"/>
+      <c r="E42" s="192"/>
+      <c r="F42" s="192"/>
+      <c r="G42" s="192"/>
+      <c r="H42" s="32">
+        <f>+H32+H33</f>
+        <v>1490766.71</v>
+      </c>
+      <c r="J42" s="167"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+    </row>
+    <row r="44" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="35">
-        <f>H40</f>
-        <v>110800</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="201" t="s">
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="35">
+        <f>H39</f>
+        <v>445500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+    </row>
+    <row r="46" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="202"/>
-      <c r="C47" s="202"/>
-      <c r="D47" s="202"/>
-      <c r="E47" s="202"/>
-      <c r="F47" s="202"/>
-      <c r="G47" s="202"/>
-      <c r="H47" s="203"/>
-    </row>
-    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="193" t="s">
+      <c r="B46" s="202"/>
+      <c r="C46" s="202"/>
+      <c r="D46" s="202"/>
+      <c r="E46" s="202"/>
+      <c r="F46" s="202"/>
+      <c r="G46" s="202"/>
+      <c r="H46" s="203"/>
+    </row>
+    <row r="47" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="193" t="s">
         <v>152</v>
       </c>
-      <c r="B48" s="193"/>
-      <c r="C48" s="193"/>
-      <c r="D48" s="193"/>
-      <c r="E48" s="193"/>
-      <c r="F48" s="193"/>
-      <c r="G48" s="193"/>
-      <c r="H48" s="41">
-        <v>1833318.3077273103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B47" s="193"/>
+      <c r="C47" s="193"/>
+      <c r="D47" s="193"/>
+      <c r="E47" s="193"/>
+      <c r="F47" s="193"/>
+      <c r="G47" s="193"/>
+      <c r="H47" s="41">
+        <v>2237684.7725573108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="45">
+        <f>Planilla!I31</f>
+        <v>1986523.3583134203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B49" s="37"/>
       <c r="C49" s="37"/>
@@ -2799,58 +2799,43 @@
       <c r="E49" s="37"/>
       <c r="F49" s="37"/>
       <c r="G49" s="37"/>
-      <c r="H49" s="45">
-        <f>Planilla!I31</f>
-        <v>1987845.22483</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="38">
-        <f>-(H33+H40)</f>
-        <v>-1993721.36</v>
-      </c>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A51" s="39" t="s">
+      <c r="H49" s="38">
+        <f>-(H32+H39)</f>
+        <v>-1936266.71</v>
+      </c>
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A50" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="49">
-        <f>SUM(H48:H50)</f>
-        <v>1827442.1725573104</v>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="49">
+        <f>SUM(H47:H49)</f>
+        <v>2287941.4208707316</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A35:H36"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A34:H35"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2867,30 +2852,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" style="53" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="55" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="54" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" style="54" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" style="54" customWidth="1"/>
-    <col min="10" max="10" width="0.109375" style="54" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" style="54" customWidth="1"/>
-    <col min="12" max="12" width="0.109375" style="54" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="53" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="55" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="54" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="54" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="54" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" style="54" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="54" customWidth="1"/>
+    <col min="12" max="12" width="0.140625" style="54" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="221" t="str">
         <f>Gastos!E7</f>
         <v xml:space="preserve">PERIODO: SEPTIEMBRE </v>
@@ -2913,10 +2898,10 @@
       <c r="Q1" s="222"/>
       <c r="R1" s="223"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="92"/>
       <c r="C2" s="183">
-        <v>1472678.76</v>
+        <v>1490766.71</v>
       </c>
       <c r="G2" s="56"/>
       <c r="H2" s="56"/>
@@ -2926,10 +2911,10 @@
       <c r="L2" s="13"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
       <c r="D3" s="183">
-        <v>513573.92</v>
+        <v>533528.66</v>
       </c>
       <c r="G3" s="56"/>
       <c r="H3" s="56"/>
@@ -2938,7 +2923,7 @@
       <c r="L3" s="90"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="C4" s="13" t="s">
         <v>158</v>
@@ -2956,12 +2941,12 @@
       <c r="Q4" s="219"/>
       <c r="R4" s="220"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="91"/>
       <c r="C5" s="229">
         <f>D3</f>
-        <v>513573.92</v>
+        <v>533528.66</v>
       </c>
       <c r="D5" s="229"/>
       <c r="E5" s="13"/>
@@ -2973,7 +2958,7 @@
       <c r="M5" s="17"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="88"/>
       <c r="C6" s="13" t="s">
         <v>157</v>
@@ -2988,12 +2973,12 @@
       <c r="L6" s="56"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="88"/>
       <c r="B7" s="87"/>
       <c r="C7" s="229">
         <f>C2-D3</f>
-        <v>959104.84000000008</v>
+        <v>957238.04999999993</v>
       </c>
       <c r="D7" s="229"/>
       <c r="E7" s="89"/>
@@ -3005,7 +2990,7 @@
       <c r="L7" s="56"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="88"/>
       <c r="B8" s="87"/>
       <c r="C8" s="87" t="s">
@@ -3021,11 +3006,11 @@
       <c r="L8" s="56"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="86"/>
       <c r="B9" s="85"/>
       <c r="C9" s="230">
-        <v>110000</v>
+        <v>445500</v>
       </c>
       <c r="D9" s="230"/>
       <c r="E9" s="84"/>
@@ -3043,7 +3028,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="80" t="s">
         <v>32</v>
       </c>
@@ -3099,7 +3084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="174" t="s">
         <v>81</v>
       </c>
@@ -3115,14 +3100,14 @@
         <v>7.9</v>
       </c>
       <c r="G11" s="67">
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="H11" s="67">
         <v>0</v>
       </c>
       <c r="I11" s="67">
         <f>G11</f>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="J11" s="67" t="e">
         <f>C8*F11/100</f>
@@ -3143,25 +3128,25 @@
       </c>
       <c r="O11" s="67">
         <f>C$7*F11/100</f>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P11" s="67">
         <f>C$9*F11/100</f>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q11" s="67">
         <f>C$5*F11/100</f>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R11" s="179">
         <f t="shared" ref="R11:R29" si="2">O11+N11+P11+Q11</f>
-        <v>125031.62204000002</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U11" s="93" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="168" t="s">
         <v>82</v>
       </c>
@@ -3177,14 +3162,14 @@
         <v>7.9</v>
       </c>
       <c r="G12" s="159">
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="H12" s="159">
         <v>0</v>
       </c>
       <c r="I12" s="67">
         <f>G12</f>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="J12" s="159" t="e">
         <f>C8*F12/100</f>
@@ -3205,25 +3190,25 @@
       </c>
       <c r="O12" s="159">
         <f t="shared" ref="O12:O29" si="4">C$7*F12/100</f>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P12" s="67">
         <f t="shared" ref="P12:P29" si="5">C$9*F12/100</f>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q12" s="67">
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R12" s="165">
         <f t="shared" si="2"/>
-        <v>125031.62204000002</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U12" s="94" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="160" t="s">
         <v>83</v>
       </c>
@@ -3241,50 +3226,53 @@
         <v>7.9</v>
       </c>
       <c r="G13" s="67">
-        <v>126809.33181271916</v>
+        <v>255645.23380710077</v>
       </c>
       <c r="H13" s="159">
         <v>0</v>
       </c>
-      <c r="I13" s="67"/>
+      <c r="I13" s="67">
+        <f>G13</f>
+        <v>255645.23380710077</v>
+      </c>
       <c r="J13" s="159" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K13" s="159">
         <f t="shared" si="0"/>
-        <v>126809.33181271916</v>
+        <v>0</v>
       </c>
       <c r="L13" s="159"/>
       <c r="M13" s="165">
         <f t="shared" si="3"/>
-        <v>3804.2799543815745</v>
+        <v>0</v>
       </c>
       <c r="N13" s="165">
         <f t="shared" si="1"/>
-        <v>130613.61176710074</v>
+        <v>0</v>
       </c>
       <c r="O13" s="159">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P13" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q13" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R13" s="165">
         <f t="shared" si="2"/>
-        <v>255645.23380710077</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U13" s="94" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="110" t="s">
         <v>84</v>
       </c>
@@ -3300,12 +3288,12 @@
         <v>7.9</v>
       </c>
       <c r="G14" s="158">
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="H14" s="74"/>
       <c r="I14" s="67">
         <f>G14</f>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="J14" s="65" t="e">
         <f>C8*F14/100</f>
@@ -3326,25 +3314,25 @@
       </c>
       <c r="O14" s="65">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P14" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q14" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R14" s="64">
         <f t="shared" si="2"/>
-        <v>125031.62204000002</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U14" s="94" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="110" t="s">
         <v>85</v>
       </c>
@@ -3360,50 +3348,53 @@
         <v>7.9</v>
       </c>
       <c r="G15" s="72">
-        <v>275141.40676182072</v>
+        <v>408427.27100467531</v>
       </c>
       <c r="H15" s="74">
         <v>0</v>
       </c>
-      <c r="I15" s="67"/>
+      <c r="I15" s="67">
+        <f>G15</f>
+        <v>408427.27100467531</v>
+      </c>
       <c r="J15" s="65" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K15" s="65">
         <f t="shared" si="0"/>
-        <v>275141.40676182072</v>
+        <v>0</v>
       </c>
       <c r="L15" s="65"/>
       <c r="M15" s="64">
         <f t="shared" si="3"/>
-        <v>8254.2422028546207</v>
+        <v>0</v>
       </c>
       <c r="N15" s="64">
         <f t="shared" si="1"/>
-        <v>283395.64896467532</v>
+        <v>0</v>
       </c>
       <c r="O15" s="65">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P15" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q15" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R15" s="64">
         <f t="shared" si="2"/>
-        <v>408427.27100467531</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U15" s="94" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="160" t="s">
         <v>86</v>
       </c>
@@ -3421,14 +3412,14 @@
         <v>7.9</v>
       </c>
       <c r="G16" s="67">
-        <v>126809.89046926852</v>
+        <v>125031.34985144658</v>
       </c>
       <c r="H16" s="159">
         <v>0</v>
       </c>
       <c r="I16" s="67">
-        <f>136056-I28</f>
-        <v>126810.15472999999</v>
+        <f>G16</f>
+        <v>125031.34985144658</v>
       </c>
       <c r="J16" s="159" t="e">
         <f>C8*F16/100</f>
@@ -3436,38 +3427,38 @@
       </c>
       <c r="K16" s="159">
         <f t="shared" si="0"/>
-        <v>-0.26426073147740681</v>
+        <v>0</v>
       </c>
       <c r="L16" s="159"/>
       <c r="M16" s="165">
         <f t="shared" si="3"/>
-        <v>-7.9278219443222036E-3</v>
+        <v>0</v>
       </c>
       <c r="N16" s="165">
         <f t="shared" si="1"/>
-        <v>-0.27218855342172898</v>
+        <v>0</v>
       </c>
       <c r="O16" s="159">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P16" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q16" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R16" s="165">
         <f t="shared" si="2"/>
-        <v>125031.34985144658</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U16" s="94" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="110" t="s">
         <v>87</v>
       </c>
@@ -3485,14 +3476,14 @@
         <v>7.9</v>
       </c>
       <c r="G17" s="72">
-        <v>126809.97612170172</v>
+        <v>125031.43807345279</v>
       </c>
       <c r="H17" s="65">
         <v>0</v>
       </c>
       <c r="I17" s="67">
-        <f>136056-I23</f>
-        <v>126810.15472999999</v>
+        <f>G17</f>
+        <v>125031.43807345279</v>
       </c>
       <c r="J17" s="65" t="e">
         <f>C8*F17/100</f>
@@ -3500,38 +3491,38 @@
       </c>
       <c r="K17" s="65">
         <f t="shared" si="0"/>
-        <v>-0.17860829827259295</v>
+        <v>0</v>
       </c>
       <c r="L17" s="65"/>
       <c r="M17" s="64">
         <f t="shared" si="3"/>
-        <v>-5.3582489481777884E-3</v>
+        <v>0</v>
       </c>
       <c r="N17" s="64">
         <f t="shared" si="1"/>
-        <v>-0.18396654722077074</v>
+        <v>0</v>
       </c>
       <c r="O17" s="65">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P17" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q17" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R17" s="64">
         <f t="shared" si="2"/>
-        <v>125031.43807345279</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U17" s="94" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="160" t="s">
         <v>88</v>
       </c>
@@ -3549,14 +3540,14 @@
         <v>7.9</v>
       </c>
       <c r="G18" s="67">
-        <v>607774.55649808713</v>
+        <v>124838.38386877713</v>
       </c>
       <c r="H18" s="159">
         <v>0</v>
       </c>
       <c r="I18" s="67">
-        <f>637000-I26</f>
-        <v>607962.16637306078</v>
+        <f>G18</f>
+        <v>124838.38386877713</v>
       </c>
       <c r="J18" s="159" t="e">
         <f>C8*F18/100</f>
@@ -3564,38 +3555,38 @@
       </c>
       <c r="K18" s="159">
         <f t="shared" si="0"/>
-        <v>-187.60987497365568</v>
+        <v>0</v>
       </c>
       <c r="L18" s="159"/>
       <c r="M18" s="165">
         <f t="shared" si="3"/>
-        <v>-5.6282962492096704</v>
+        <v>0</v>
       </c>
       <c r="N18" s="165">
         <f t="shared" si="1"/>
-        <v>-193.23817122286536</v>
+        <v>0</v>
       </c>
       <c r="O18" s="159">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P18" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q18" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R18" s="165">
         <f t="shared" si="2"/>
-        <v>124838.38386877713</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U18" s="94" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="160" t="s">
         <v>89</v>
       </c>
@@ -3611,13 +3602,14 @@
         <v>7.9</v>
       </c>
       <c r="G19" s="67">
-        <v>126697.01361356268</v>
+        <v>125025.47008393914</v>
       </c>
       <c r="H19" s="159">
         <v>0</v>
       </c>
       <c r="I19" s="67">
-        <v>126700</v>
+        <f>G19</f>
+        <v>125025.47008393914</v>
       </c>
       <c r="J19" s="159" t="e">
         <f>C8*F19/100</f>
@@ -3625,41 +3617,41 @@
       </c>
       <c r="K19" s="159">
         <f t="shared" ref="K19:K29" si="7">G19-H19-I19</f>
-        <v>-2.9863864373182878</v>
+        <v>0</v>
       </c>
       <c r="L19" s="159">
         <f>G19-I19</f>
-        <v>-2.9863864373182878</v>
+        <v>0</v>
       </c>
       <c r="M19" s="165">
         <f t="shared" si="3"/>
-        <v>-0.17918318623909726</v>
+        <v>0</v>
       </c>
       <c r="N19" s="165">
         <f t="shared" si="1"/>
-        <v>-6.1519560608756727</v>
+        <v>0</v>
       </c>
       <c r="O19" s="159">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P19" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q19" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R19" s="165">
         <f t="shared" si="2"/>
-        <v>125025.47008393914</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U19" s="94" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="110" t="s">
         <v>90</v>
       </c>
@@ -3675,12 +3667,12 @@
         <v>7.9</v>
       </c>
       <c r="G20" s="72">
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="H20" s="65"/>
       <c r="I20" s="67">
         <f>G20</f>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="J20" s="65"/>
       <c r="K20" s="65">
@@ -3698,25 +3690,25 @@
       </c>
       <c r="O20" s="65">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P20" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q20" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R20" s="64">
         <f t="shared" si="2"/>
-        <v>125031.62204000002</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U20" s="94" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="160" t="s">
         <v>91</v>
       </c>
@@ -3734,48 +3726,48 @@
         <v>7.9</v>
       </c>
       <c r="G21" s="67">
-        <v>126809.03557658312</v>
+        <v>120968.14931198064</v>
       </c>
       <c r="H21" s="159"/>
       <c r="I21" s="67">
-        <f>140000-I24</f>
-        <v>130754.15472999999</v>
+        <f>G21</f>
+        <v>120968.14931198064</v>
       </c>
       <c r="J21" s="159"/>
       <c r="K21" s="159">
         <f t="shared" si="7"/>
-        <v>-3945.1191534168756</v>
+        <v>0</v>
       </c>
       <c r="L21" s="159"/>
       <c r="M21" s="165">
         <f t="shared" si="3"/>
-        <v>-118.35357460250627</v>
+        <v>0</v>
       </c>
       <c r="N21" s="165">
         <f t="shared" si="8"/>
-        <v>-4063.472728019382</v>
+        <v>0</v>
       </c>
       <c r="O21" s="159">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P21" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q21" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R21" s="165">
         <f t="shared" si="2"/>
-        <v>120968.14931198064</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="U21" s="94" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="160" t="s">
         <v>92</v>
       </c>
@@ -3793,49 +3785,49 @@
         <v>7.9</v>
       </c>
       <c r="G22" s="67">
-        <v>275141.69642020005</v>
+        <v>125031.53639642705</v>
       </c>
       <c r="H22" s="159"/>
       <c r="I22" s="67">
-        <f>295548-I29</f>
-        <v>275141.77956930001</v>
+        <f>G22</f>
+        <v>125031.53639642705</v>
       </c>
       <c r="J22" s="159"/>
       <c r="K22" s="159">
         <f t="shared" si="7"/>
-        <v>-8.3149099955335259E-2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="159"/>
       <c r="M22" s="165">
         <f t="shared" si="3"/>
-        <v>-2.4944729986600576E-3</v>
+        <v>0</v>
       </c>
       <c r="N22" s="165">
         <f t="shared" si="8"/>
-        <v>-8.5643572953995314E-2</v>
+        <v>0</v>
       </c>
       <c r="O22" s="159">
         <f t="shared" si="4"/>
-        <v>75769.282360000012</v>
+        <v>75621.805949999994</v>
       </c>
       <c r="P22" s="67">
         <f t="shared" si="5"/>
-        <v>8690</v>
+        <v>35194.5</v>
       </c>
       <c r="Q22" s="67">
         <f t="shared" si="6"/>
-        <v>40572.339679999997</v>
+        <v>42148.764140000007</v>
       </c>
       <c r="R22" s="165">
         <f t="shared" si="2"/>
-        <v>125031.53639642705</v>
+        <v>152965.07008999999</v>
       </c>
       <c r="S22" s="180"/>
       <c r="U22" s="94" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="110"/>
       <c r="B23" s="71"/>
       <c r="C23" s="94" t="s">
@@ -3852,12 +3844,12 @@
         <v>0.74</v>
       </c>
       <c r="G23" s="72">
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="H23" s="65"/>
       <c r="I23" s="67">
         <f>G23</f>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65">
@@ -3875,22 +3867,22 @@
       </c>
       <c r="O23" s="65">
         <f t="shared" si="4"/>
-        <v>7097.3758160000007</v>
+        <v>7083.5615699999989</v>
       </c>
       <c r="P23" s="67">
         <f t="shared" si="5"/>
-        <v>814</v>
+        <v>3296.7</v>
       </c>
       <c r="Q23" s="65"/>
       <c r="R23" s="64">
         <f t="shared" si="2"/>
-        <v>7911.3758160000007</v>
+        <v>10380.261569999999</v>
       </c>
       <c r="U23" s="94" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="160"/>
       <c r="B24" s="161"/>
       <c r="C24" s="95" t="s">
@@ -3907,12 +3899,12 @@
         <v>0.74</v>
       </c>
       <c r="G24" s="67">
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="H24" s="159"/>
       <c r="I24" s="67">
         <f>G24</f>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="J24" s="159"/>
       <c r="K24" s="159">
@@ -3930,11 +3922,11 @@
       </c>
       <c r="O24" s="159">
         <f t="shared" si="4"/>
-        <v>7097.3758160000007</v>
+        <v>7083.5615699999989</v>
       </c>
       <c r="P24" s="67">
         <f t="shared" si="5"/>
-        <v>814</v>
+        <v>3296.7</v>
       </c>
       <c r="Q24" s="159">
         <f>'Calculo Servicios  (2)'!H22</f>
@@ -3942,13 +3934,13 @@
       </c>
       <c r="R24" s="165">
         <f t="shared" si="2"/>
-        <v>7911.3758160000007</v>
+        <v>10380.261569999999</v>
       </c>
       <c r="U24" s="94" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="110"/>
       <c r="B25" s="71"/>
       <c r="C25" s="94" t="s">
@@ -3963,12 +3955,12 @@
         <v>0.74</v>
       </c>
       <c r="G25" s="72">
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="H25" s="65"/>
       <c r="I25" s="67">
         <f t="shared" ref="I25" si="9">G25</f>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="J25" s="65"/>
       <c r="K25" s="65">
@@ -3986,11 +3978,11 @@
       </c>
       <c r="O25" s="65">
         <f t="shared" si="4"/>
-        <v>7097.3758160000007</v>
+        <v>7083.5615699999989</v>
       </c>
       <c r="P25" s="67">
         <f t="shared" si="5"/>
-        <v>814</v>
+        <v>3296.7</v>
       </c>
       <c r="Q25" s="65">
         <f>'Calculo Servicios  (2)'!H23</f>
@@ -3998,13 +3990,13 @@
       </c>
       <c r="R25" s="64">
         <f t="shared" si="2"/>
-        <v>7911.3758160000007</v>
+        <v>10380.261569999999</v>
       </c>
       <c r="U25" s="94" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="160"/>
       <c r="B26" s="157"/>
       <c r="C26" s="95" t="s">
@@ -4021,14 +4013,14 @@
         <v>0.74</v>
       </c>
       <c r="G26" s="67">
-        <v>29037.833626939202</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="H26" s="159">
         <v>0</v>
       </c>
       <c r="I26" s="67">
         <f>G26</f>
-        <v>29037.833626939202</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="J26" s="159" t="e">
         <f>C8*F26/100</f>
@@ -4049,11 +4041,11 @@
       </c>
       <c r="O26" s="159">
         <f t="shared" si="4"/>
-        <v>7097.3758160000007</v>
+        <v>7083.5615699999989</v>
       </c>
       <c r="P26" s="67">
         <f t="shared" si="5"/>
-        <v>814</v>
+        <v>3296.7</v>
       </c>
       <c r="Q26" s="159">
         <f>'Calculo Servicios  (2)'!H24</f>
@@ -4061,13 +4053,13 @@
       </c>
       <c r="R26" s="165">
         <f t="shared" si="2"/>
-        <v>7911.3758160000007</v>
+        <v>10380.261569999999</v>
       </c>
       <c r="U26" s="94" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="110"/>
       <c r="B27" s="71"/>
       <c r="C27" s="94" t="s">
@@ -4082,36 +4074,39 @@
         <v>0.74</v>
       </c>
       <c r="G27" s="72">
-        <v>20406.220430700003</v>
+        <v>28929.782859621002</v>
       </c>
       <c r="H27" s="65">
         <v>0</v>
       </c>
-      <c r="I27" s="67"/>
+      <c r="I27" s="67">
+        <f>G27</f>
+        <v>28929.782859621002</v>
+      </c>
       <c r="J27" s="65" t="e">
         <f>C8*F27/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K27" s="65">
         <f t="shared" si="7"/>
-        <v>20406.220430700003</v>
+        <v>0</v>
       </c>
       <c r="L27" s="65"/>
       <c r="M27" s="64">
         <f t="shared" si="3"/>
-        <v>612.18661292100012</v>
+        <v>0</v>
       </c>
       <c r="N27" s="64">
         <f t="shared" si="8"/>
-        <v>21018.407043621002</v>
+        <v>0</v>
       </c>
       <c r="O27" s="65">
         <f t="shared" si="4"/>
-        <v>7097.3758160000007</v>
+        <v>7083.5615699999989</v>
       </c>
       <c r="P27" s="67">
         <f t="shared" si="5"/>
-        <v>814</v>
+        <v>3296.7</v>
       </c>
       <c r="Q27" s="65">
         <f>'Calculo Servicios  (2)'!H25</f>
@@ -4119,13 +4114,13 @@
       </c>
       <c r="R27" s="64">
         <f t="shared" si="2"/>
-        <v>28929.782859621002</v>
+        <v>10380.261569999999</v>
       </c>
       <c r="U27" s="94" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="184"/>
       <c r="B28" s="185"/>
       <c r="C28" s="95" t="s">
@@ -4142,14 +4137,14 @@
         <v>0.74</v>
       </c>
       <c r="G28" s="67">
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="H28" s="67">
         <v>0</v>
       </c>
       <c r="I28" s="67">
         <f>G28</f>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="J28" s="67">
         <v>0</v>
@@ -4169,11 +4164,11 @@
       </c>
       <c r="O28" s="67">
         <f t="shared" si="4"/>
-        <v>7097.3758160000007</v>
+        <v>7083.5615699999989</v>
       </c>
       <c r="P28" s="67">
         <f t="shared" si="5"/>
-        <v>814</v>
+        <v>3296.7</v>
       </c>
       <c r="Q28" s="67">
         <f>'Calculo Servicios  (2)'!H26</f>
@@ -4181,13 +4176,13 @@
       </c>
       <c r="R28" s="179">
         <f t="shared" si="2"/>
-        <v>7911.3758160000007</v>
+        <v>10380.261569999999</v>
       </c>
       <c r="U28" s="94" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="160"/>
       <c r="B29" s="173"/>
       <c r="C29" s="95" t="s">
@@ -4204,14 +4199,14 @@
         <v>0.74</v>
       </c>
       <c r="G29" s="67">
-        <v>20406.220430700003</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="H29" s="159">
         <v>0</v>
       </c>
       <c r="I29" s="67">
         <f>G29</f>
-        <v>20406.220430700003</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="J29" s="159" t="e">
         <f>C8*F29/100</f>
@@ -4232,11 +4227,11 @@
       </c>
       <c r="O29" s="159">
         <f t="shared" si="4"/>
-        <v>7097.3758160000007</v>
+        <v>7083.5615699999989</v>
       </c>
       <c r="P29" s="67">
         <f t="shared" si="5"/>
-        <v>814</v>
+        <v>3296.7</v>
       </c>
       <c r="Q29" s="159">
         <f>'Calculo Servicios  (2)'!H27</f>
@@ -4244,13 +4239,13 @@
       </c>
       <c r="R29" s="165">
         <f t="shared" si="2"/>
-        <v>7911.3758160000007</v>
+        <v>10380.261569999999</v>
       </c>
       <c r="U29" s="95" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="73"/>
       <c r="B30" s="71"/>
       <c r="C30" s="70"/>
@@ -4278,7 +4273,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="227"/>
       <c r="B31" s="228"/>
       <c r="C31" s="228"/>
@@ -4287,7 +4282,7 @@
       <c r="F31" s="97"/>
       <c r="G31" s="61">
         <f>SUM(G11:G30)</f>
-        <v>2406065.9424022823</v>
+        <v>1986523.3583134203</v>
       </c>
       <c r="H31" s="61">
         <f>SUM(H11:H30)</f>
@@ -4295,37 +4290,37 @@
       </c>
       <c r="I31" s="62">
         <f>SUM(I11:I30)</f>
-        <v>1987845.22483</v>
+        <v>1986523.3583134203</v>
       </c>
       <c r="J31" s="61"/>
       <c r="K31" s="62">
         <f>SUM(K11:K30)</f>
-        <v>418220.71757228236</v>
+        <v>0</v>
       </c>
       <c r="L31" s="61"/>
       <c r="M31" s="60"/>
       <c r="N31" s="59"/>
       <c r="O31" s="62">
         <f>SUM(O11:O30)</f>
-        <v>958913.01903200068</v>
+        <v>957046.6023899999</v>
       </c>
       <c r="P31" s="62">
         <f>SUM(P11:P29)</f>
-        <v>109978</v>
+        <v>445410.90000000008</v>
       </c>
       <c r="Q31" s="62">
         <f>SUM(Q11:Q29)</f>
-        <v>486868.07615999988</v>
+        <v>505785.16967999999</v>
       </c>
       <c r="R31" s="62">
         <f>SUM(R11:R29)</f>
-        <v>1986523.3583134203</v>
+        <v>1908242.672070001</v>
       </c>
       <c r="U31" s="94" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="224" t="s">
         <v>19</v>
       </c>
@@ -4349,7 +4344,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
       <c r="F33" s="57"/>
       <c r="G33" s="56"/>
       <c r="H33" s="56"/>
@@ -4363,7 +4358,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C34" s="218"/>
       <c r="D34" s="218"/>
       <c r="E34" s="218"/>
@@ -4378,7 +4373,7 @@
       <c r="N34" s="218"/>
       <c r="O34" s="218"/>
     </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C35" s="218"/>
       <c r="D35" s="218"/>
       <c r="E35" s="218"/>
@@ -4393,7 +4388,7 @@
       <c r="N35" s="218"/>
       <c r="O35" s="218"/>
     </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C36" s="218"/>
       <c r="D36" s="218"/>
       <c r="E36" s="218"/>
@@ -4408,7 +4403,7 @@
       <c r="N36" s="218"/>
       <c r="O36" s="218"/>
     </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C37" s="218"/>
       <c r="D37" s="218"/>
       <c r="E37" s="218"/>
@@ -4423,7 +4418,7 @@
       <c r="N37" s="218"/>
       <c r="O37" s="218"/>
     </row>
-    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="218"/>
       <c r="D38" s="218"/>
       <c r="E38" s="218"/>
@@ -4458,22 +4453,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="114" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="114" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.44140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="114" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="114" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="114" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.44140625" style="114"/>
-    <col min="13" max="13" width="14.6640625" style="114" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="114" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" style="114"/>
+    <col min="9" max="12" width="11.42578125" style="114"/>
+    <col min="13" max="13" width="14.7109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="114" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="114"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="231" t="s">
         <v>80</v>
       </c>
@@ -4482,7 +4477,7 @@
       <c r="D1" s="232"/>
       <c r="E1" s="233"/>
     </row>
-    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="155"/>
       <c r="B2" s="140"/>
       <c r="C2" s="140"/>
@@ -4491,7 +4486,7 @@
       </c>
       <c r="E2" s="151"/>
     </row>
-    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="153">
         <f>13+28+19</f>
         <v>60</v>
@@ -4513,28 +4508,28 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="150"/>
       <c r="B4" s="149"/>
       <c r="C4" s="149"/>
       <c r="D4" s="149"/>
       <c r="E4" s="148"/>
     </row>
-    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="147"/>
       <c r="B5" s="147"/>
       <c r="C5" s="147"/>
       <c r="D5" s="147"/>
       <c r="E5" s="147"/>
     </row>
-    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="147"/>
       <c r="B6" s="147"/>
       <c r="C6" s="147"/>
       <c r="D6" s="147"/>
       <c r="E6" s="147"/>
     </row>
-    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="234" t="s">
         <v>77</v>
       </c>
@@ -4552,7 +4547,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="107">
         <v>400523.88</v>
       </c>
@@ -4588,7 +4583,7 @@
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="143" t="s">
         <v>34</v>
       </c>
@@ -4637,7 +4632,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="141" t="s">
         <v>35</v>
       </c>
@@ -4686,7 +4681,7 @@
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="141" t="s">
         <v>36</v>
       </c>
@@ -4734,7 +4729,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="141" t="s">
         <v>37</v>
       </c>
@@ -4781,7 +4776,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="141" t="s">
         <v>38</v>
       </c>
@@ -4824,7 +4819,7 @@
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="141" t="s">
         <v>39</v>
       </c>
@@ -4859,7 +4854,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="141" t="s">
         <v>40</v>
       </c>
@@ -4898,7 +4893,7 @@
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="141" t="s">
         <v>41</v>
       </c>
@@ -4933,7 +4928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="141" t="s">
         <v>42</v>
       </c>
@@ -4968,7 +4963,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="141" t="s">
         <v>43</v>
       </c>
@@ -5003,7 +4998,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="141" t="s">
         <v>44</v>
       </c>
@@ -5038,7 +5033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="141" t="s">
         <v>45</v>
       </c>
@@ -5070,7 +5065,7 @@
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="139" t="s">
         <v>139</v>
       </c>
@@ -5092,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="100">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
@@ -5102,7 +5097,7 @@
       </c>
       <c r="L22" s="134"/>
     </row>
-    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="99">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
@@ -5111,23 +5106,23 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="132"/>
       <c r="J25" s="114">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="J26" s="114">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J27" s="114">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B28" s="237" t="s">
         <v>138</v>
       </c>
@@ -5139,7 +5134,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="131" t="s">
         <v>137</v>
       </c>
@@ -5159,7 +5154,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="125" t="s">
         <v>132</v>
       </c>
@@ -5182,7 +5177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="125" t="s">
         <v>131</v>
       </c>
@@ -5201,7 +5196,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B32" s="125" t="s">
         <v>130</v>
       </c>
@@ -5220,7 +5215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="125" t="s">
         <v>129</v>
       </c>
@@ -5243,7 +5238,7 @@
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B34" s="125" t="s">
         <v>128</v>
       </c>
@@ -5262,7 +5257,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="125" t="s">
         <v>127</v>
       </c>
@@ -5281,7 +5276,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="125" t="s">
         <v>126</v>
       </c>
@@ -5300,7 +5295,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="125" t="s">
         <v>125</v>
       </c>
@@ -5316,7 +5311,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B38" s="125" t="s">
         <v>124</v>
       </c>
@@ -5338,7 +5333,7 @@
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="125" t="s">
         <v>122</v>
       </c>
@@ -5352,7 +5347,7 @@
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B40" s="125" t="s">
         <v>121</v>
       </c>
@@ -5366,7 +5361,7 @@
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B41" s="125" t="s">
         <v>120</v>
       </c>
@@ -5380,7 +5375,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B42" s="125" t="s">
         <v>119</v>
       </c>
@@ -5394,7 +5389,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B43" s="125" t="s">
         <v>118</v>
       </c>
@@ -5408,7 +5403,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B44" s="122" t="s">
         <v>117</v>
       </c>
@@ -5422,7 +5417,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B45" s="122" t="s">
         <v>116</v>
       </c>
@@ -5436,7 +5431,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B46" s="122" t="s">
         <v>115</v>
       </c>
@@ -5450,7 +5445,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="118" t="s">
         <v>114</v>
       </c>

--- a/TUCUMAN 1061/Septiembre/tucuman Septiembre.xlsx
+++ b/TUCUMAN 1061/Septiembre/tucuman Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9604F5B8-6C80-482F-A0DE-EC1712BCF21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03015B6-014B-4F87-9ED0-BB6385034CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="168">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -567,6 +567,11 @@
   </si>
   <si>
     <t xml:space="preserve">Adelanto Sr. Leo trabajo en medianera </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco santander - C DE P TUCUMAN 1061 1063 - Nro. De cuenta : 39-022068/6
+CBU: 0720039720000002206868
+</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1369,7 @@
     <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1413,7 +1418,6 @@
     <xf numFmtId="8" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1661,15 +1665,24 @@
     <xf numFmtId="6" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1741,9 +1754,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1835,15 +1845,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>168275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>681875</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1872,8 +1882,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="104775" y="142875"/>
-          <a:ext cx="2101100" cy="857249"/>
+          <a:off x="0" y="168275"/>
+          <a:ext cx="2325158" cy="1127125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2203,220 +2213,222 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="D1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>112</v>
+      </c>
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="D2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>112</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E2" s="192">
+        <v>1153202676</v>
+      </c>
+      <c r="F2" s="192"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="D3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="194">
-        <v>1153202676</v>
-      </c>
-      <c r="F3" s="194"/>
+        <v>2</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>113</v>
+      </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="D4" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>113</v>
+      <c r="D4" t="s">
+        <v>17</v>
       </c>
       <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J4" s="191"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="D5" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D5" s="193" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="193"/>
+      <c r="F5" s="193"/>
+      <c r="G5" s="193"/>
+      <c r="H5" s="194"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="D6" s="193"/>
+      <c r="E6" s="193"/>
+      <c r="F6" s="193"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="194"/>
+    </row>
+    <row r="7" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="D7" s="193"/>
+      <c r="E7" s="193"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="193"/>
+      <c r="H7" s="194"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="204" t="s">
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="206" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="204"/>
-      <c r="C12" s="204"/>
-      <c r="D12" s="204"/>
-      <c r="E12" s="204"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="204"/>
-      <c r="H12" s="204"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>143</v>
-      </c>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
+      <c r="F13" s="206"/>
+      <c r="G13" s="206"/>
+      <c r="H13" s="206"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="189">
-        <f>392270+392270*2%</f>
-        <v>400115.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="98" t="s">
-        <v>163</v>
-      </c>
-      <c r="B15" s="19"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>143</v>
+      </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="189">
+      <c r="H15" s="188">
+        <f>392270+392270*2%</f>
+        <v>400115.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="188">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="181">
-        <f>SUM(H13:H15)</f>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="180">
+        <f>SUM(H14:H16)</f>
         <v>404145.68000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="43"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="205" t="s">
+    <row r="18" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="42"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="206"/>
-      <c r="C18" s="206"/>
-      <c r="D18" s="206"/>
-      <c r="E18" s="206"/>
-      <c r="F18" s="206"/>
-      <c r="G18" s="206"/>
-      <c r="H18" s="207"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="B19" s="208"/>
+      <c r="C19" s="208"/>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="208"/>
+      <c r="G19" s="208"/>
+      <c r="H19" s="209"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
         <v>59</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="26">
-        <v>364854.17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>58</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="25"/>
@@ -2425,373 +2437,372 @@
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
       <c r="H20" s="26">
+        <v>364854.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="26">
         <v>533528.86</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="27">
-        <f>SUM(H19:H20)</f>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="27">
+        <f>SUM(H20:H21)</f>
         <v>898383.03</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="208" t="s">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="210" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="208"/>
-      <c r="C22" s="208"/>
-      <c r="D22" s="208"/>
-      <c r="E22" s="208"/>
-      <c r="F22" s="208"/>
-      <c r="G22" s="208"/>
-      <c r="H22" s="208"/>
-      <c r="J22" s="26"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="98" t="s">
+      <c r="B23" s="210"/>
+      <c r="C23" s="210"/>
+      <c r="D23" s="210"/>
+      <c r="E23" s="210"/>
+      <c r="F23" s="210"/>
+      <c r="G23" s="210"/>
+      <c r="H23" s="210"/>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="97" t="s">
         <v>142</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="26">
-        <v>46638</v>
-      </c>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-    </row>
-    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="98" t="s">
-        <v>144</v>
-      </c>
       <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="26">
+        <v>46638</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="97" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="26">
         <v>75000</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="27">
-        <f>SUM(H23:H24)</f>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="27">
+        <f>SUM(H24:H25)</f>
         <v>121638</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="205" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="207" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="206"/>
-      <c r="C26" s="206"/>
-      <c r="D26" s="206"/>
-      <c r="E26" s="206"/>
-      <c r="F26" s="206"/>
-      <c r="G26" s="206"/>
-      <c r="H26" s="207"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="B27" s="208"/>
+      <c r="C27" s="208"/>
+      <c r="D27" s="208"/>
+      <c r="E27" s="208"/>
+      <c r="F27" s="208"/>
+      <c r="G27" s="208"/>
+      <c r="H27" s="209"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19" t="s">
+      <c r="B28" s="19"/>
+      <c r="C28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="44"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="43"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="190">
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="189">
         <v>66600</v>
       </c>
-      <c r="I28" s="44"/>
-      <c r="N28" t="s">
+      <c r="I29" s="43"/>
+      <c r="N29" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="29"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="205" t="s">
+    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="29"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="207" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="206"/>
-      <c r="C30" s="206"/>
-      <c r="D30" s="206"/>
-      <c r="E30" s="206"/>
-      <c r="F30" s="206"/>
-      <c r="G30" s="206"/>
-      <c r="H30" s="207"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="50"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="52"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="B31" s="208"/>
+      <c r="C31" s="208"/>
+      <c r="D31" s="208"/>
+      <c r="E31" s="208"/>
+      <c r="F31" s="208"/>
+      <c r="G31" s="208"/>
+      <c r="H31" s="209"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="49"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="51"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32">
-        <f>H16+H21+H25+H28+H31</f>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32">
+        <f>H17+H22+H26+H29+H32</f>
         <v>1490766.71</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="46" t="s">
+    <row r="34" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A34" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
-    </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="195" t="s">
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
+    </row>
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="197" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="196"/>
-      <c r="C34" s="196"/>
-      <c r="D34" s="196"/>
-      <c r="E34" s="196"/>
-      <c r="F34" s="196"/>
-      <c r="G34" s="196"/>
-      <c r="H34" s="197"/>
-      <c r="I34" s="167"/>
-      <c r="K34" s="167"/>
-    </row>
-    <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="198"/>
-      <c r="B35" s="199"/>
-      <c r="C35" s="199"/>
-      <c r="D35" s="199"/>
-      <c r="E35" s="199"/>
-      <c r="F35" s="199"/>
-      <c r="G35" s="199"/>
-      <c r="H35" s="200"/>
-    </row>
-    <row r="36" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="209" t="s">
+      <c r="B35" s="198"/>
+      <c r="C35" s="198"/>
+      <c r="D35" s="198"/>
+      <c r="E35" s="198"/>
+      <c r="F35" s="198"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="199"/>
+      <c r="I35" s="166"/>
+      <c r="K35" s="166"/>
+    </row>
+    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="200"/>
+      <c r="B36" s="201"/>
+      <c r="C36" s="201"/>
+      <c r="D36" s="201"/>
+      <c r="E36" s="201"/>
+      <c r="F36" s="201"/>
+      <c r="G36" s="201"/>
+      <c r="H36" s="202"/>
+    </row>
+    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="211" t="s">
         <v>165</v>
       </c>
-      <c r="B36" s="210"/>
-      <c r="C36" s="210"/>
-      <c r="D36" s="210"/>
-      <c r="E36" s="210"/>
-      <c r="F36" s="210"/>
-      <c r="G36" s="211"/>
-      <c r="H36" s="191">
+      <c r="B37" s="212"/>
+      <c r="C37" s="212"/>
+      <c r="D37" s="212"/>
+      <c r="E37" s="212"/>
+      <c r="F37" s="212"/>
+      <c r="G37" s="213"/>
+      <c r="H37" s="190">
         <v>45500</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="209" t="s">
+    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="211" t="s">
         <v>166</v>
       </c>
-      <c r="B37" s="210"/>
-      <c r="C37" s="210"/>
-      <c r="D37" s="210"/>
-      <c r="E37" s="210"/>
-      <c r="F37" s="210"/>
-      <c r="G37" s="211"/>
-      <c r="H37" s="191">
+      <c r="B38" s="212"/>
+      <c r="C38" s="212"/>
+      <c r="D38" s="212"/>
+      <c r="E38" s="212"/>
+      <c r="F38" s="212"/>
+      <c r="G38" s="213"/>
+      <c r="H38" s="190">
         <v>400000</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="212"/>
-      <c r="B38" s="213"/>
-      <c r="C38" s="213"/>
-      <c r="D38" s="213"/>
-      <c r="E38" s="213"/>
-      <c r="F38" s="213"/>
-      <c r="G38" s="214"/>
-      <c r="H38" s="33"/>
-    </row>
-    <row r="39" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="215" t="s">
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="214"/>
+      <c r="B39" s="215"/>
+      <c r="C39" s="215"/>
+      <c r="D39" s="215"/>
+      <c r="E39" s="215"/>
+      <c r="F39" s="215"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="33"/>
+    </row>
+    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="217" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="216"/>
-      <c r="C39" s="216"/>
-      <c r="D39" s="216"/>
-      <c r="E39" s="216"/>
-      <c r="F39" s="216"/>
-      <c r="G39" s="217"/>
-      <c r="H39" s="34">
-        <f>SUM(H36:H38)</f>
+      <c r="B40" s="218"/>
+      <c r="C40" s="218"/>
+      <c r="D40" s="218"/>
+      <c r="E40" s="218"/>
+      <c r="F40" s="218"/>
+      <c r="G40" s="219"/>
+      <c r="H40" s="34">
+        <f>SUM(H37:H39)</f>
         <v>445500</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="187"/>
-      <c r="B40" s="187"/>
-      <c r="C40" s="187"/>
-      <c r="D40" s="187"/>
-      <c r="E40" s="187"/>
-      <c r="F40" s="187"/>
-      <c r="G40" s="187"/>
-      <c r="H40" s="188"/>
-    </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H41" s="19"/>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="192" t="s">
+    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="186"/>
+      <c r="B41" s="186"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="186"/>
+      <c r="E41" s="186"/>
+      <c r="F41" s="186"/>
+      <c r="G41" s="186"/>
+      <c r="H41" s="187"/>
+    </row>
+    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="19"/>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="195" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="192"/>
-      <c r="C42" s="192"/>
-      <c r="D42" s="192"/>
-      <c r="E42" s="192"/>
-      <c r="F42" s="192"/>
-      <c r="G42" s="192"/>
-      <c r="H42" s="32">
-        <f>+H32+H33</f>
+      <c r="B43" s="195"/>
+      <c r="C43" s="195"/>
+      <c r="D43" s="195"/>
+      <c r="E43" s="195"/>
+      <c r="F43" s="195"/>
+      <c r="G43" s="195"/>
+      <c r="H43" s="32">
+        <f>+H33+H34</f>
         <v>1490766.71</v>
       </c>
-      <c r="J42" s="167"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="30" t="s">
+      <c r="J43" s="166"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+    </row>
+    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="35">
-        <f>H39</f>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="35">
+        <f>H40</f>
         <v>445500</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-    </row>
-    <row r="46" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="201" t="s">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+    </row>
+    <row r="47" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="203" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="202"/>
-      <c r="C46" s="202"/>
-      <c r="D46" s="202"/>
-      <c r="E46" s="202"/>
-      <c r="F46" s="202"/>
-      <c r="G46" s="202"/>
-      <c r="H46" s="203"/>
-    </row>
-    <row r="47" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="193" t="s">
+      <c r="B47" s="204"/>
+      <c r="C47" s="204"/>
+      <c r="D47" s="204"/>
+      <c r="E47" s="204"/>
+      <c r="F47" s="204"/>
+      <c r="G47" s="204"/>
+      <c r="H47" s="205"/>
+    </row>
+    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="196" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="193"/>
-      <c r="C47" s="193"/>
-      <c r="D47" s="193"/>
-      <c r="E47" s="193"/>
-      <c r="F47" s="193"/>
-      <c r="G47" s="193"/>
-      <c r="H47" s="41">
+      <c r="B48" s="196"/>
+      <c r="C48" s="196"/>
+      <c r="D48" s="196"/>
+      <c r="E48" s="196"/>
+      <c r="F48" s="196"/>
+      <c r="G48" s="196"/>
+      <c r="H48" s="41">
         <v>2237684.7725573108</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="36" t="s">
         <v>149</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="45">
-        <f>Planilla!I31</f>
-        <v>1986523.3583134203</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="36" t="s">
-        <v>150</v>
       </c>
       <c r="B49" s="37"/>
       <c r="C49" s="37"/>
@@ -2799,50 +2810,63 @@
       <c r="E49" s="37"/>
       <c r="F49" s="37"/>
       <c r="G49" s="37"/>
-      <c r="H49" s="38">
-        <f>-(H32+H39)</f>
+      <c r="H49" s="44">
+        <f>Planilla!I31</f>
+        <v>1986523.3583134203</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="38">
+        <f>-(H33+H40)</f>
         <v>-1936266.71</v>
       </c>
-      <c r="J49" s="15"/>
-    </row>
-    <row r="50" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A50" s="39" t="s">
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A51" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="40"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="49">
-        <f>SUM(H47:H49)</f>
+      <c r="B51" s="40"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="48">
+        <f>SUM(H48:H50)</f>
         <v>2287941.4208707316</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A34:H35"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A36:G36"/>
+  <mergeCells count="15">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D5:H7"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A35:H36"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A37:G37"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="95" orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2852,175 +2876,175 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="53" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="55" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="54" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="54" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="54" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" style="54" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="54" customWidth="1"/>
-    <col min="12" max="12" width="0.140625" style="54" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" style="52" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="54" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="53" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" style="53" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="53" customWidth="1"/>
+    <col min="10" max="10" width="0.109375" style="53" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" style="53" customWidth="1"/>
+    <col min="12" max="12" width="0.109375" style="53" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="221" t="str">
-        <f>Gastos!E7</f>
+    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="222" t="str">
+        <f>Gastos!E8</f>
         <v xml:space="preserve">PERIODO: SEPTIEMBRE </v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="223"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="92"/>
-      <c r="C2" s="183">
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="224"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="91"/>
+      <c r="C2" s="182">
         <v>1490766.71</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
       <c r="L2" s="13"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="88"/>
-      <c r="D3" s="183">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="87"/>
+      <c r="D3" s="182">
         <v>533528.66</v>
       </c>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="L3" s="90"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="L3" s="89"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="88"/>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="87"/>
       <c r="C4" s="13" t="s">
         <v>158</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="219"/>
-      <c r="N4" s="219"/>
-      <c r="O4" s="219"/>
-      <c r="P4" s="219"/>
-      <c r="Q4" s="219"/>
-      <c r="R4" s="220"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="88"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="229">
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="192"/>
+      <c r="N4" s="192"/>
+      <c r="O4" s="192"/>
+      <c r="P4" s="192"/>
+      <c r="Q4" s="192"/>
+      <c r="R4" s="221"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="87"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="230">
         <f>D3</f>
         <v>533528.66</v>
       </c>
-      <c r="D5" s="229"/>
+      <c r="D5" s="230"/>
       <c r="E5" s="13"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="L5" s="90"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="L5" s="89"/>
       <c r="M5" s="17"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="88"/>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="87"/>
       <c r="C6" s="13" t="s">
         <v>157</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="88"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="229">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="87"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="230">
         <f>C2-D3</f>
         <v>957238.04999999993</v>
       </c>
-      <c r="D7" s="229"/>
-      <c r="E7" s="89"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
+      <c r="D7" s="230"/>
+      <c r="E7" s="88"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="88"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87" t="s">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="87"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="86"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="230">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="85"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="231">
         <v>445500</v>
       </c>
-      <c r="D9" s="230"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="81"/>
+      <c r="D9" s="231"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
+      <c r="L9" s="80"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3028,1410 +3052,1410 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="80" t="s">
+    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="79" t="s">
+      <c r="D10" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="79" t="s">
+      <c r="E10" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="78" t="s">
+      <c r="F10" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="77" t="s">
+      <c r="G10" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="77" t="s">
+      <c r="H10" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="77" t="s">
+      <c r="I10" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="77" t="s">
+      <c r="J10" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="77" t="s">
+      <c r="K10" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="77" t="s">
+      <c r="L10" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="76" t="s">
+      <c r="M10" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="N10" s="76" t="s">
+      <c r="N10" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="76" t="s">
+      <c r="O10" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="P10" s="76" t="s">
+      <c r="P10" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="76" t="s">
+      <c r="Q10" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="76" t="s">
+      <c r="R10" s="75" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="174" t="s">
+    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="173" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="175"/>
-      <c r="C11" s="176" t="s">
+      <c r="B11" s="174"/>
+      <c r="C11" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="177" t="s">
+      <c r="D11" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="163"/>
-      <c r="F11" s="178">
+      <c r="E11" s="162"/>
+      <c r="F11" s="177">
         <v>7.9</v>
       </c>
-      <c r="G11" s="67">
+      <c r="G11" s="66">
         <v>125031.62204000002</v>
       </c>
-      <c r="H11" s="67">
-        <v>0</v>
-      </c>
-      <c r="I11" s="67">
-        <f>G11</f>
+      <c r="H11" s="66">
+        <v>0</v>
+      </c>
+      <c r="I11" s="66">
+        <f t="shared" ref="I11:I24" si="0">G11</f>
         <v>125031.62204000002</v>
       </c>
-      <c r="J11" s="67" t="e">
+      <c r="J11" s="66" t="e">
         <f>C8*F11/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="67">
-        <f t="shared" ref="K11:K18" si="0">G11-H11-I11</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="67"/>
-      <c r="M11" s="179">
+      <c r="K11" s="66">
+        <f t="shared" ref="K11:K18" si="1">G11-H11-I11</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="66"/>
+      <c r="M11" s="178">
         <f>(K11+L11)*3%</f>
         <v>0</v>
       </c>
-      <c r="N11" s="179">
-        <f t="shared" ref="N11:N19" si="1">K11+M11+L11</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="67">
+      <c r="N11" s="178">
+        <f t="shared" ref="N11:N19" si="2">K11+M11+L11</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="66">
         <f>C$7*F11/100</f>
         <v>75621.805949999994</v>
       </c>
-      <c r="P11" s="67">
+      <c r="P11" s="66">
         <f>C$9*F11/100</f>
         <v>35194.5</v>
       </c>
-      <c r="Q11" s="67">
+      <c r="Q11" s="66">
         <f>C$5*F11/100</f>
         <v>42148.764140000007</v>
       </c>
-      <c r="R11" s="179">
-        <f t="shared" ref="R11:R29" si="2">O11+N11+P11+Q11</f>
+      <c r="R11" s="178">
+        <f t="shared" ref="R11:R29" si="3">O11+N11+P11+Q11</f>
         <v>152965.07008999999</v>
       </c>
-      <c r="U11" s="93" t="s">
+      <c r="U11" s="92" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="168" t="s">
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="167" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="161"/>
-      <c r="C12" s="169" t="s">
+      <c r="B12" s="160"/>
+      <c r="C12" s="168" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="170" t="s">
+      <c r="D12" s="169" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="171"/>
-      <c r="F12" s="172">
+      <c r="E12" s="170"/>
+      <c r="F12" s="171">
         <v>7.9</v>
       </c>
-      <c r="G12" s="159">
+      <c r="G12" s="158">
         <v>125031.62204000002</v>
       </c>
-      <c r="H12" s="159">
-        <v>0</v>
-      </c>
-      <c r="I12" s="67">
-        <f>G12</f>
+      <c r="H12" s="158">
+        <v>0</v>
+      </c>
+      <c r="I12" s="66">
+        <f t="shared" si="0"/>
         <v>125031.62204000002</v>
       </c>
-      <c r="J12" s="159" t="e">
+      <c r="J12" s="158" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="159">
+      <c r="K12" s="158">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="158"/>
+      <c r="M12" s="164">
+        <f t="shared" ref="M12:M29" si="4">(K12+L12)*3%</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="164">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="158">
+        <f t="shared" ref="O12:O29" si="5">C$7*F12/100</f>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P12" s="66">
+        <f t="shared" ref="P12:P29" si="6">C$9*F12/100</f>
+        <v>35194.5</v>
+      </c>
+      <c r="Q12" s="66">
+        <f t="shared" ref="Q12:Q22" si="7">C$5*F12/100</f>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R12" s="164">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U12" s="93" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="159" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="160"/>
+      <c r="C13" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="161" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="162" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="163">
+        <v>7.9</v>
+      </c>
+      <c r="G13" s="66">
+        <v>255645.23380710077</v>
+      </c>
+      <c r="H13" s="158">
+        <v>0</v>
+      </c>
+      <c r="I13" s="66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="159"/>
-      <c r="M12" s="165">
-        <f t="shared" ref="M12:M29" si="3">(K12+L12)*3%</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="165">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="159">
-        <f t="shared" ref="O12:O29" si="4">C$7*F12/100</f>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P12" s="67">
-        <f t="shared" ref="P12:P29" si="5">C$9*F12/100</f>
-        <v>35194.5</v>
-      </c>
-      <c r="Q12" s="67">
-        <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R12" s="165">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U12" s="94" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="160" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="161"/>
-      <c r="C13" s="95" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="162" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="163" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="164">
-        <v>7.9</v>
-      </c>
-      <c r="G13" s="67">
         <v>255645.23380710077</v>
       </c>
-      <c r="H13" s="159">
-        <v>0</v>
-      </c>
-      <c r="I13" s="67">
-        <f>G13</f>
-        <v>255645.23380710077</v>
-      </c>
-      <c r="J13" s="159" t="e">
+      <c r="J13" s="158" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="159">
+      <c r="K13" s="158">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="158"/>
+      <c r="M13" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="164">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="158">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P13" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q13" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R13" s="164">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U13" s="93" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="109" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="74"/>
+      <c r="C14" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="155" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="95">
+        <v>7.9</v>
+      </c>
+      <c r="G14" s="157">
+        <v>125031.62204000002</v>
+      </c>
+      <c r="H14" s="73"/>
+      <c r="I14" s="66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="159"/>
-      <c r="M13" s="165">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="165">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="159">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P13" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q13" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R13" s="165">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U13" s="94" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="110" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="75"/>
-      <c r="C14" s="94" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="156" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="113"/>
-      <c r="F14" s="96">
-        <v>7.9</v>
-      </c>
-      <c r="G14" s="158">
         <v>125031.62204000002</v>
       </c>
-      <c r="H14" s="74"/>
-      <c r="I14" s="67">
-        <f>G14</f>
-        <v>125031.62204000002</v>
-      </c>
-      <c r="J14" s="65" t="e">
+      <c r="J14" s="64" t="e">
         <f>C8*F14/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K14" s="65">
+      <c r="K14" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="65"/>
+      <c r="M14" s="63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="64">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P14" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q14" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R14" s="63">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U14" s="93" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="70"/>
+      <c r="C15" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="110" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="112"/>
+      <c r="F15" s="95">
+        <v>7.9</v>
+      </c>
+      <c r="G15" s="71">
+        <v>408427.27100467531</v>
+      </c>
+      <c r="H15" s="73">
+        <v>0</v>
+      </c>
+      <c r="I15" s="66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="66"/>
-      <c r="M14" s="64">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="65">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P14" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q14" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R14" s="64">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U14" s="94" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="110" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="111" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="113"/>
-      <c r="F15" s="96">
-        <v>7.9</v>
-      </c>
-      <c r="G15" s="72">
         <v>408427.27100467531</v>
       </c>
-      <c r="H15" s="74">
-        <v>0</v>
-      </c>
-      <c r="I15" s="67">
-        <f>G15</f>
-        <v>408427.27100467531</v>
-      </c>
-      <c r="J15" s="65" t="e">
+      <c r="J15" s="64" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="65">
+      <c r="K15" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="64"/>
+      <c r="M15" s="63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="64">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P15" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q15" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R15" s="63">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U15" s="93" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="159" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="160"/>
+      <c r="C16" s="94" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="161" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="162" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="163">
+        <v>7.9</v>
+      </c>
+      <c r="G16" s="66">
+        <v>125031.34985144658</v>
+      </c>
+      <c r="H16" s="158">
+        <v>0</v>
+      </c>
+      <c r="I16" s="66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="65"/>
-      <c r="M15" s="64">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="65">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P15" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q15" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R15" s="64">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U15" s="94" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="160" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="161"/>
-      <c r="C16" s="95" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="162" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" s="163" t="s">
-        <v>161</v>
-      </c>
-      <c r="F16" s="164">
-        <v>7.9</v>
-      </c>
-      <c r="G16" s="67">
         <v>125031.34985144658</v>
       </c>
-      <c r="H16" s="159">
-        <v>0</v>
-      </c>
-      <c r="I16" s="67">
-        <f>G16</f>
-        <v>125031.34985144658</v>
-      </c>
-      <c r="J16" s="159" t="e">
+      <c r="J16" s="158" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="159">
+      <c r="K16" s="158">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="158"/>
+      <c r="M16" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="164">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="158">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P16" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q16" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R16" s="164">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U16" s="93" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="109" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="70"/>
+      <c r="C17" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="110" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="112" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="95">
+        <v>7.9</v>
+      </c>
+      <c r="G17" s="71">
+        <v>125031.43807345279</v>
+      </c>
+      <c r="H17" s="64">
+        <v>0</v>
+      </c>
+      <c r="I17" s="66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="159"/>
-      <c r="M16" s="165">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="165">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="159">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P16" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q16" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R16" s="165">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U16" s="94" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="110" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="94" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="111" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="113" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="96">
-        <v>7.9</v>
-      </c>
-      <c r="G17" s="72">
         <v>125031.43807345279</v>
       </c>
-      <c r="H17" s="65">
-        <v>0</v>
-      </c>
-      <c r="I17" s="67">
-        <f>G17</f>
-        <v>125031.43807345279</v>
-      </c>
-      <c r="J17" s="65" t="e">
+      <c r="J17" s="64" t="e">
         <f>C8*F17/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="65">
+      <c r="K17" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="64"/>
+      <c r="M17" s="63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="64">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P17" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q17" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R17" s="63">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U17" s="93" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="159" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="160"/>
+      <c r="C18" s="94" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="161" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="162" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" s="163">
+        <v>7.9</v>
+      </c>
+      <c r="G18" s="66">
+        <v>124838.38386877713</v>
+      </c>
+      <c r="H18" s="158">
+        <v>0</v>
+      </c>
+      <c r="I18" s="66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="65"/>
-      <c r="M17" s="64">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="65">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P17" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q17" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R17" s="64">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U17" s="94" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="160" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="161"/>
-      <c r="C18" s="95" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="162" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="163" t="s">
-        <v>147</v>
-      </c>
-      <c r="F18" s="164">
-        <v>7.9</v>
-      </c>
-      <c r="G18" s="67">
         <v>124838.38386877713</v>
       </c>
-      <c r="H18" s="159">
-        <v>0</v>
-      </c>
-      <c r="I18" s="67">
-        <f>G18</f>
-        <v>124838.38386877713</v>
-      </c>
-      <c r="J18" s="159" t="e">
+      <c r="J18" s="158" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="159">
+      <c r="K18" s="158">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="158"/>
+      <c r="M18" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="164">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="158">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P18" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q18" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R18" s="164">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U18" s="93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="159" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="160"/>
+      <c r="C19" s="94" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="161" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="162"/>
+      <c r="F19" s="163">
+        <v>7.9</v>
+      </c>
+      <c r="G19" s="66">
+        <v>125025.47008393914</v>
+      </c>
+      <c r="H19" s="158">
+        <v>0</v>
+      </c>
+      <c r="I19" s="66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="159"/>
-      <c r="M18" s="165">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="165">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="159">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P18" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q18" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R18" s="165">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U18" s="94" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="160" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="161"/>
-      <c r="C19" s="95" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="162" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="163"/>
-      <c r="F19" s="164">
-        <v>7.9</v>
-      </c>
-      <c r="G19" s="67">
         <v>125025.47008393914</v>
       </c>
-      <c r="H19" s="159">
-        <v>0</v>
-      </c>
-      <c r="I19" s="67">
-        <f>G19</f>
-        <v>125025.47008393914</v>
-      </c>
-      <c r="J19" s="159" t="e">
+      <c r="J19" s="158" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="159">
-        <f t="shared" ref="K19:K29" si="7">G19-H19-I19</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="159">
+      <c r="K19" s="158">
+        <f t="shared" ref="K19:K29" si="8">G19-H19-I19</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="158">
         <f>G19-I19</f>
         <v>0</v>
       </c>
-      <c r="M19" s="165">
+      <c r="M19" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="164">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="158">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P19" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q19" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R19" s="164">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="165">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="159">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U19" s="93" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="109" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="70"/>
+      <c r="C20" s="93" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="110" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="95">
+        <v>7.9</v>
+      </c>
+      <c r="G20" s="71">
+        <v>125031.62204000002</v>
+      </c>
+      <c r="H20" s="64"/>
+      <c r="I20" s="66">
+        <f t="shared" si="0"/>
+        <v>125031.62204000002</v>
+      </c>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="64"/>
+      <c r="M20" s="63">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="63">
+        <f t="shared" ref="N20:N29" si="9">K20+M20+L20</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="64">
+        <f t="shared" si="5"/>
         <v>75621.805949999994</v>
       </c>
-      <c r="P19" s="67">
+      <c r="P20" s="66">
+        <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q20" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R20" s="63">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U20" s="93" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="159" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="160"/>
+      <c r="C21" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="161" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="162" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="163">
+        <v>7.9</v>
+      </c>
+      <c r="G21" s="66">
+        <v>120968.14931198064</v>
+      </c>
+      <c r="H21" s="158"/>
+      <c r="I21" s="66">
+        <f t="shared" si="0"/>
+        <v>120968.14931198064</v>
+      </c>
+      <c r="J21" s="158"/>
+      <c r="K21" s="158">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="158"/>
+      <c r="M21" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="158">
         <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P21" s="66">
+        <f t="shared" si="6"/>
         <v>35194.5</v>
       </c>
-      <c r="Q19" s="67">
+      <c r="Q21" s="66">
+        <f t="shared" si="7"/>
+        <v>42148.764140000007</v>
+      </c>
+      <c r="R21" s="164">
+        <f t="shared" si="3"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="U21" s="93" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="159" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="160"/>
+      <c r="C22" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="161" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22" s="162" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="163">
+        <v>7.9</v>
+      </c>
+      <c r="G22" s="66">
+        <v>125031.53639642705</v>
+      </c>
+      <c r="H22" s="158"/>
+      <c r="I22" s="66">
+        <f t="shared" si="0"/>
+        <v>125031.53639642705</v>
+      </c>
+      <c r="J22" s="158"/>
+      <c r="K22" s="158">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="158"/>
+      <c r="M22" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="158">
+        <f t="shared" si="5"/>
+        <v>75621.805949999994</v>
+      </c>
+      <c r="P22" s="66">
         <f t="shared" si="6"/>
+        <v>35194.5</v>
+      </c>
+      <c r="Q22" s="66">
+        <f t="shared" si="7"/>
         <v>42148.764140000007</v>
       </c>
-      <c r="R19" s="165">
-        <f t="shared" si="2"/>
+      <c r="R22" s="164">
+        <f t="shared" si="3"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="U19" s="94" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="110" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="111" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" s="113"/>
-      <c r="F20" s="96">
-        <v>7.9</v>
-      </c>
-      <c r="G20" s="72">
-        <v>125031.62204000002</v>
-      </c>
-      <c r="H20" s="65"/>
-      <c r="I20" s="67">
-        <f>G20</f>
-        <v>125031.62204000002</v>
-      </c>
-      <c r="J20" s="65"/>
-      <c r="K20" s="65">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="65"/>
-      <c r="M20" s="64">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="64">
-        <f t="shared" ref="N20:N29" si="8">K20+M20+L20</f>
-        <v>0</v>
-      </c>
-      <c r="O20" s="65">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P20" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q20" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R20" s="64">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U20" s="94" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="161"/>
-      <c r="C21" s="95" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="162" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" s="163" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="164">
-        <v>7.9</v>
-      </c>
-      <c r="G21" s="67">
-        <v>120968.14931198064</v>
-      </c>
-      <c r="H21" s="159"/>
-      <c r="I21" s="67">
-        <f>G21</f>
-        <v>120968.14931198064</v>
-      </c>
-      <c r="J21" s="159"/>
-      <c r="K21" s="159">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="159"/>
-      <c r="M21" s="165">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="165">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="159">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P21" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q21" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R21" s="165">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U21" s="94" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="161"/>
-      <c r="C22" s="95" t="s">
+      <c r="S22" s="179"/>
+      <c r="U22" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="162" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" s="163" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="164">
-        <v>7.9</v>
-      </c>
-      <c r="G22" s="67">
-        <v>125031.53639642705</v>
-      </c>
-      <c r="H22" s="159"/>
-      <c r="I22" s="67">
-        <f>G22</f>
-        <v>125031.53639642705</v>
-      </c>
-      <c r="J22" s="159"/>
-      <c r="K22" s="159">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="159"/>
-      <c r="M22" s="165">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="165">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="159">
-        <f t="shared" si="4"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P22" s="67">
-        <f t="shared" si="5"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q22" s="67">
-        <f t="shared" si="6"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R22" s="165">
-        <f t="shared" si="2"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="S22" s="180"/>
-      <c r="U22" s="94" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="110"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="94" t="s">
+    </row>
+    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="109"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="112" t="str">
+      <c r="D23" s="111" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="113" t="s">
+      <c r="E23" s="112" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="96">
+      <c r="F23" s="95">
         <v>0.74</v>
       </c>
-      <c r="G23" s="72">
+      <c r="G23" s="71">
         <v>7911.3758160000007</v>
       </c>
-      <c r="H23" s="65"/>
-      <c r="I23" s="67">
-        <f>G23</f>
+      <c r="H23" s="64"/>
+      <c r="I23" s="66">
+        <f t="shared" si="0"/>
         <v>7911.3758160000007</v>
       </c>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="65"/>
-      <c r="M23" s="64">
+      <c r="J23" s="64"/>
+      <c r="K23" s="64">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="64"/>
+      <c r="M23" s="63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="63">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="64">
+        <f t="shared" si="5"/>
+        <v>7083.5615699999989</v>
+      </c>
+      <c r="P23" s="66">
+        <f t="shared" si="6"/>
+        <v>3296.7</v>
+      </c>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="64">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="65">
-        <f t="shared" si="4"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P23" s="67">
-        <f t="shared" si="5"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="64">
-        <f t="shared" si="2"/>
         <v>10380.261569999999</v>
       </c>
-      <c r="U23" s="94" t="s">
+      <c r="U23" s="93" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160"/>
-      <c r="B24" s="161"/>
-      <c r="C24" s="95" t="s">
+    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="159"/>
+      <c r="B24" s="160"/>
+      <c r="C24" s="94" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="166" t="str">
+      <c r="D24" s="165" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="163" t="s">
+      <c r="E24" s="162" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="164">
+      <c r="F24" s="163">
         <v>0.74</v>
       </c>
-      <c r="G24" s="67">
+      <c r="G24" s="66">
         <v>7911.3758160000007</v>
       </c>
-      <c r="H24" s="159"/>
-      <c r="I24" s="67">
-        <f>G24</f>
+      <c r="H24" s="158"/>
+      <c r="I24" s="66">
+        <f t="shared" si="0"/>
         <v>7911.3758160000007</v>
       </c>
-      <c r="J24" s="159"/>
-      <c r="K24" s="159">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="159"/>
-      <c r="M24" s="165">
+      <c r="J24" s="158"/>
+      <c r="K24" s="158">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="158"/>
+      <c r="M24" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="158">
+        <f t="shared" si="5"/>
+        <v>7083.5615699999989</v>
+      </c>
+      <c r="P24" s="66">
+        <f t="shared" si="6"/>
+        <v>3296.7</v>
+      </c>
+      <c r="Q24" s="158">
+        <f>'Calculo Servicios  (2)'!H22</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="164">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="165">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="159">
-        <f t="shared" si="4"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P24" s="67">
-        <f t="shared" si="5"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q24" s="159">
-        <f>'Calculo Servicios  (2)'!H22</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="165">
-        <f t="shared" si="2"/>
         <v>10380.261569999999</v>
       </c>
-      <c r="U24" s="94" t="s">
+      <c r="U24" s="93" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="110"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="94" t="s">
+    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="109"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="112" t="str">
+      <c r="D25" s="111" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="96">
+      <c r="E25" s="111"/>
+      <c r="F25" s="95">
         <v>0.74</v>
       </c>
-      <c r="G25" s="72">
+      <c r="G25" s="71">
         <v>7911.3758160000007</v>
       </c>
-      <c r="H25" s="65"/>
-      <c r="I25" s="67">
-        <f t="shared" ref="I25" si="9">G25</f>
+      <c r="H25" s="64"/>
+      <c r="I25" s="66">
+        <f t="shared" ref="I25" si="10">G25</f>
         <v>7911.3758160000007</v>
       </c>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="65"/>
-      <c r="M25" s="64">
+      <c r="J25" s="64"/>
+      <c r="K25" s="64">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="64"/>
+      <c r="M25" s="63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="63">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="64">
+        <f t="shared" si="5"/>
+        <v>7083.5615699999989</v>
+      </c>
+      <c r="P25" s="66">
+        <f t="shared" si="6"/>
+        <v>3296.7</v>
+      </c>
+      <c r="Q25" s="64">
+        <f>'Calculo Servicios  (2)'!H23</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="64">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="65">
-        <f t="shared" si="4"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P25" s="67">
-        <f t="shared" si="5"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q25" s="65">
-        <f>'Calculo Servicios  (2)'!H23</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="64">
-        <f t="shared" si="2"/>
         <v>10380.261569999999</v>
       </c>
-      <c r="U25" s="94" t="s">
+      <c r="U25" s="93" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160"/>
-      <c r="B26" s="157"/>
-      <c r="C26" s="95" t="s">
+    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="159"/>
+      <c r="B26" s="156"/>
+      <c r="C26" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="166" t="str">
+      <c r="D26" s="165" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="163" t="s">
+      <c r="E26" s="162" t="s">
         <v>147</v>
       </c>
-      <c r="F26" s="164">
+      <c r="F26" s="163">
         <v>0.74</v>
       </c>
-      <c r="G26" s="67">
+      <c r="G26" s="66">
         <v>7911.3758160000007</v>
       </c>
-      <c r="H26" s="159">
-        <v>0</v>
-      </c>
-      <c r="I26" s="67">
+      <c r="H26" s="158">
+        <v>0</v>
+      </c>
+      <c r="I26" s="66">
         <f>G26</f>
         <v>7911.3758160000007</v>
       </c>
-      <c r="J26" s="159" t="e">
+      <c r="J26" s="158" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="159">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="159"/>
-      <c r="M26" s="165">
+      <c r="K26" s="158">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="158"/>
+      <c r="M26" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="158">
+        <f t="shared" si="5"/>
+        <v>7083.5615699999989</v>
+      </c>
+      <c r="P26" s="66">
+        <f t="shared" si="6"/>
+        <v>3296.7</v>
+      </c>
+      <c r="Q26" s="158">
+        <f>'Calculo Servicios  (2)'!H24</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="164">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="165">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="159">
-        <f t="shared" si="4"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P26" s="67">
-        <f t="shared" si="5"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q26" s="159">
-        <f>'Calculo Servicios  (2)'!H24</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="165">
-        <f t="shared" si="2"/>
         <v>10380.261569999999</v>
       </c>
-      <c r="U26" s="94" t="s">
+      <c r="U26" s="93" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="110"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="94" t="s">
+    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="109"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="112" t="str">
+      <c r="D27" s="111" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="112"/>
-      <c r="F27" s="96">
+      <c r="E27" s="111"/>
+      <c r="F27" s="95">
         <v>0.74</v>
       </c>
-      <c r="G27" s="72">
+      <c r="G27" s="71">
         <v>28929.782859621002</v>
       </c>
-      <c r="H27" s="65">
-        <v>0</v>
-      </c>
-      <c r="I27" s="67">
+      <c r="H27" s="64">
+        <v>0</v>
+      </c>
+      <c r="I27" s="66">
         <f>G27</f>
         <v>28929.782859621002</v>
       </c>
-      <c r="J27" s="65" t="e">
+      <c r="J27" s="64" t="e">
         <f>C8*F27/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K27" s="65">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="65"/>
-      <c r="M27" s="64">
+      <c r="K27" s="64">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="64"/>
+      <c r="M27" s="63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="63">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="64">
+        <f t="shared" si="5"/>
+        <v>7083.5615699999989</v>
+      </c>
+      <c r="P27" s="66">
+        <f t="shared" si="6"/>
+        <v>3296.7</v>
+      </c>
+      <c r="Q27" s="64">
+        <f>'Calculo Servicios  (2)'!H25</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N27" s="64">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="65">
-        <f t="shared" si="4"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P27" s="67">
-        <f t="shared" si="5"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q27" s="65">
-        <f>'Calculo Servicios  (2)'!H25</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="64">
-        <f t="shared" si="2"/>
         <v>10380.261569999999</v>
       </c>
-      <c r="U27" s="94" t="s">
+      <c r="U27" s="93" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="184"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="95" t="s">
+    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="183"/>
+      <c r="B28" s="184"/>
+      <c r="C28" s="94" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="166" t="str">
+      <c r="D28" s="165" t="str">
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="163" t="s">
+      <c r="E28" s="162" t="s">
         <v>161</v>
       </c>
-      <c r="F28" s="186">
+      <c r="F28" s="185">
         <v>0.74</v>
       </c>
-      <c r="G28" s="67">
+      <c r="G28" s="66">
         <v>7911.3758160000007</v>
       </c>
-      <c r="H28" s="67">
-        <v>0</v>
-      </c>
-      <c r="I28" s="67">
+      <c r="H28" s="66">
+        <v>0</v>
+      </c>
+      <c r="I28" s="66">
         <f>G28</f>
         <v>7911.3758160000007</v>
       </c>
-      <c r="J28" s="67">
-        <v>0</v>
-      </c>
-      <c r="K28" s="67">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="67"/>
-      <c r="M28" s="179">
+      <c r="J28" s="66">
+        <v>0</v>
+      </c>
+      <c r="K28" s="66">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="66"/>
+      <c r="M28" s="178">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="178">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="66">
+        <f t="shared" si="5"/>
+        <v>7083.5615699999989</v>
+      </c>
+      <c r="P28" s="66">
+        <f t="shared" si="6"/>
+        <v>3296.7</v>
+      </c>
+      <c r="Q28" s="66">
+        <f>'Calculo Servicios  (2)'!H26</f>
+        <v>0</v>
+      </c>
+      <c r="R28" s="178">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="179">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="67">
-        <f t="shared" si="4"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P28" s="67">
-        <f t="shared" si="5"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q28" s="67">
-        <f>'Calculo Servicios  (2)'!H26</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="179">
-        <f t="shared" si="2"/>
         <v>10380.261569999999</v>
       </c>
-      <c r="U28" s="94" t="s">
+      <c r="U28" s="93" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="160"/>
-      <c r="B29" s="173"/>
-      <c r="C29" s="95" t="s">
+    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="159"/>
+      <c r="B29" s="172"/>
+      <c r="C29" s="94" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="166" t="str">
+      <c r="D29" s="165" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="163" t="s">
+      <c r="E29" s="162" t="s">
         <v>153</v>
       </c>
-      <c r="F29" s="182">
+      <c r="F29" s="181">
         <v>0.74</v>
       </c>
-      <c r="G29" s="67">
+      <c r="G29" s="66">
         <v>7911.3758160000007</v>
       </c>
-      <c r="H29" s="159">
-        <v>0</v>
-      </c>
-      <c r="I29" s="67">
+      <c r="H29" s="158">
+        <v>0</v>
+      </c>
+      <c r="I29" s="66">
         <f>G29</f>
         <v>7911.3758160000007</v>
       </c>
-      <c r="J29" s="159" t="e">
+      <c r="J29" s="158" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="159">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="159"/>
-      <c r="M29" s="165">
+      <c r="K29" s="158">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="158"/>
+      <c r="M29" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="158">
+        <f t="shared" si="5"/>
+        <v>7083.5615699999989</v>
+      </c>
+      <c r="P29" s="66">
+        <f t="shared" si="6"/>
+        <v>3296.7</v>
+      </c>
+      <c r="Q29" s="158">
+        <f>'Calculo Servicios  (2)'!H27</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="164">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="165">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="159">
-        <f t="shared" si="4"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P29" s="67">
-        <f t="shared" si="5"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q29" s="159">
-        <f>'Calculo Servicios  (2)'!H27</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="165">
-        <f t="shared" si="2"/>
         <v>10380.261569999999</v>
       </c>
-      <c r="U29" s="95" t="s">
+      <c r="U29" s="94" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="73"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="65">
-        <v>0</v>
-      </c>
-      <c r="I30" s="67"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="65"/>
-      <c r="P30" s="65" t="e">
+    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="72"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="64">
+        <v>0</v>
+      </c>
+      <c r="I30" s="66"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="64" t="e">
         <f>#REF!*F30/100</f>
         <v>#REF!</v>
       </c>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="109"/>
-      <c r="U30" s="94" t="s">
+      <c r="Q30" s="64"/>
+      <c r="R30" s="108"/>
+      <c r="U30" s="93" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="227"/>
-      <c r="B31" s="228"/>
-      <c r="C31" s="228"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="61">
+    <row r="31" spans="1:21" s="57" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="228"/>
+      <c r="B31" s="229"/>
+      <c r="C31" s="229"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="60">
         <f>SUM(G11:G30)</f>
         <v>1986523.3583134203</v>
       </c>
-      <c r="H31" s="61">
+      <c r="H31" s="60">
         <f>SUM(H11:H30)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="62">
+      <c r="I31" s="61">
         <f>SUM(I11:I30)</f>
         <v>1986523.3583134203</v>
       </c>
-      <c r="J31" s="61"/>
-      <c r="K31" s="62">
+      <c r="J31" s="60"/>
+      <c r="K31" s="61">
         <f>SUM(K11:K30)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="61"/>
-      <c r="M31" s="60"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="62">
+      <c r="L31" s="60"/>
+      <c r="M31" s="59"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="61">
         <f>SUM(O11:O30)</f>
         <v>957046.6023899999</v>
       </c>
-      <c r="P31" s="62">
+      <c r="P31" s="61">
         <f>SUM(P11:P29)</f>
         <v>445410.90000000008</v>
       </c>
-      <c r="Q31" s="62">
+      <c r="Q31" s="61">
         <f>SUM(Q11:Q29)</f>
         <v>505785.16967999999</v>
       </c>
-      <c r="R31" s="62">
+      <c r="R31" s="61">
         <f>SUM(R11:R29)</f>
         <v>1908242.672070001</v>
       </c>
-      <c r="U31" s="94" t="s">
+      <c r="U31" s="93" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="224" t="s">
+    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="225" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="225"/>
-      <c r="N32" s="225"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="225"/>
-      <c r="Q32" s="225"/>
-      <c r="R32" s="226"/>
-      <c r="U32" s="94" t="s">
+      <c r="C32" s="226"/>
+      <c r="D32" s="226"/>
+      <c r="E32" s="226"/>
+      <c r="F32" s="226"/>
+      <c r="G32" s="226"/>
+      <c r="H32" s="226"/>
+      <c r="I32" s="226"/>
+      <c r="J32" s="226"/>
+      <c r="K32" s="226"/>
+      <c r="L32" s="226"/>
+      <c r="M32" s="226"/>
+      <c r="N32" s="226"/>
+      <c r="O32" s="226"/>
+      <c r="P32" s="226"/>
+      <c r="Q32" s="226"/>
+      <c r="R32" s="227"/>
+      <c r="U32" s="93" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="F33" s="57"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="56" t="s">
+    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="F33" s="56"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="L33" s="56"/>
-      <c r="U33" s="94" t="s">
+      <c r="L33" s="55"/>
+      <c r="U33" s="93" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
-      <c r="M34" s="218"/>
-      <c r="N34" s="218"/>
-      <c r="O34" s="218"/>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C35" s="218"/>
-      <c r="D35" s="218"/>
-      <c r="E35" s="218"/>
-      <c r="F35" s="218"/>
-      <c r="G35" s="218"/>
-      <c r="H35" s="218"/>
-      <c r="I35" s="218"/>
-      <c r="J35" s="218"/>
-      <c r="K35" s="218"/>
-      <c r="L35" s="218"/>
-      <c r="M35" s="218"/>
-      <c r="N35" s="218"/>
-      <c r="O35" s="218"/>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="218"/>
-      <c r="J36" s="218"/>
-      <c r="K36" s="218"/>
-      <c r="L36" s="218"/>
-      <c r="M36" s="218"/>
-      <c r="N36" s="218"/>
-      <c r="O36" s="218"/>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C37" s="218"/>
-      <c r="D37" s="218"/>
-      <c r="E37" s="218"/>
-      <c r="F37" s="218"/>
-      <c r="G37" s="218"/>
-      <c r="H37" s="218"/>
-      <c r="I37" s="218"/>
-      <c r="J37" s="218"/>
-      <c r="K37" s="218"/>
-      <c r="L37" s="218"/>
-      <c r="M37" s="218"/>
-      <c r="N37" s="218"/>
-      <c r="O37" s="218"/>
-    </row>
-    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="218"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="218"/>
-      <c r="I38" s="218"/>
-      <c r="J38" s="218"/>
-      <c r="K38" s="218"/>
-      <c r="L38" s="218"/>
-      <c r="M38" s="218"/>
-      <c r="N38" s="218"/>
-      <c r="O38" s="218"/>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C34" s="220"/>
+      <c r="D34" s="220"/>
+      <c r="E34" s="220"/>
+      <c r="F34" s="220"/>
+      <c r="G34" s="220"/>
+      <c r="H34" s="220"/>
+      <c r="I34" s="220"/>
+      <c r="J34" s="220"/>
+      <c r="K34" s="220"/>
+      <c r="L34" s="220"/>
+      <c r="M34" s="220"/>
+      <c r="N34" s="220"/>
+      <c r="O34" s="220"/>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C35" s="220"/>
+      <c r="D35" s="220"/>
+      <c r="E35" s="220"/>
+      <c r="F35" s="220"/>
+      <c r="G35" s="220"/>
+      <c r="H35" s="220"/>
+      <c r="I35" s="220"/>
+      <c r="J35" s="220"/>
+      <c r="K35" s="220"/>
+      <c r="L35" s="220"/>
+      <c r="M35" s="220"/>
+      <c r="N35" s="220"/>
+      <c r="O35" s="220"/>
+    </row>
+    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C36" s="220"/>
+      <c r="D36" s="220"/>
+      <c r="E36" s="220"/>
+      <c r="F36" s="220"/>
+      <c r="G36" s="220"/>
+      <c r="H36" s="220"/>
+      <c r="I36" s="220"/>
+      <c r="J36" s="220"/>
+      <c r="K36" s="220"/>
+      <c r="L36" s="220"/>
+      <c r="M36" s="220"/>
+      <c r="N36" s="220"/>
+      <c r="O36" s="220"/>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C37" s="220"/>
+      <c r="D37" s="220"/>
+      <c r="E37" s="220"/>
+      <c r="F37" s="220"/>
+      <c r="G37" s="220"/>
+      <c r="H37" s="220"/>
+      <c r="I37" s="220"/>
+      <c r="J37" s="220"/>
+      <c r="K37" s="220"/>
+      <c r="L37" s="220"/>
+      <c r="M37" s="220"/>
+      <c r="N37" s="220"/>
+      <c r="O37" s="220"/>
+    </row>
+    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="220"/>
+      <c r="D38" s="220"/>
+      <c r="E38" s="220"/>
+      <c r="F38" s="220"/>
+      <c r="G38" s="220"/>
+      <c r="H38" s="220"/>
+      <c r="I38" s="220"/>
+      <c r="J38" s="220"/>
+      <c r="K38" s="220"/>
+      <c r="L38" s="220"/>
+      <c r="M38" s="220"/>
+      <c r="N38" s="220"/>
+      <c r="O38" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4453,1009 +4477,1009 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="114" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="114" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="114" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.42578125" style="114"/>
-    <col min="13" max="13" width="14.7109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="114" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="114"/>
+    <col min="1" max="1" width="12.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="113" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="113" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.44140625" style="113" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="113" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.44140625" style="113"/>
+    <col min="13" max="13" width="14.6640625" style="113" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="113" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="113"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="231" t="s">
+    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="232" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="233"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="155"/>
-      <c r="B2" s="140"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="154" t="s">
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="234"/>
+    </row>
+    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="154"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="153" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="151"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="153">
+      <c r="E2" s="150"/>
+    </row>
+    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="152">
         <f>13+28+19</f>
         <v>60</v>
       </c>
-      <c r="B3" s="108">
+      <c r="B3" s="107">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="152">
+      <c r="C3" s="151">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="152">
+      <c r="D3" s="151">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="151" t="s">
+      <c r="E3" s="150" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="113" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="150"/>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="148"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="147"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-    </row>
-    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="147"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="147"/>
-      <c r="D6" s="147"/>
-      <c r="E6" s="147"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="234" t="s">
+    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="149"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="147"/>
+    </row>
+    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="146"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="146"/>
+    </row>
+    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="146"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="146"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+    </row>
+    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="235" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="235"/>
-      <c r="C7" s="235"/>
-      <c r="D7" s="235"/>
-      <c r="E7" s="235"/>
-      <c r="F7" s="235"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="236"/>
-      <c r="L7" s="114" t="s">
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="237"/>
+      <c r="L7" s="113" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="114" t="s">
+      <c r="M7" s="113" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="107">
+    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="106">
         <v>400523.88</v>
       </c>
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="144" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="145" t="s">
+      <c r="C8" s="144" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="145" t="s">
+      <c r="D8" s="144" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="146">
+      <c r="E8" s="145">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="145" t="s">
+      <c r="F8" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="145" t="s">
+      <c r="G8" s="144" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="144" t="s">
+      <c r="H8" s="143" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="140">
+      <c r="K8" s="139">
         <v>19</v>
       </c>
-      <c r="L8" s="126">
+      <c r="L8" s="125">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="126">
+      <c r="M8" s="125">
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="143" t="s">
+    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="140">
+      <c r="B9" s="139">
         <v>1617</v>
       </c>
-      <c r="C9" s="140">
+      <c r="C9" s="139">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="140">
+      <c r="D9" s="139">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
-      <c r="E9" s="104">
+      <c r="E9" s="103">
         <f>+D9/E8</f>
         <v>3.6594663278271919E-2</v>
       </c>
-      <c r="F9" s="103">
+      <c r="F9" s="102">
         <f>+A8*E9</f>
         <v>14657.036523506989</v>
       </c>
-      <c r="G9" s="103">
+      <c r="G9" s="102">
         <f>+(A8*A23)/12</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H9" s="102">
+      <c r="H9" s="101">
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="114">
+      <c r="K9" s="113">
         <v>106</v>
       </c>
-      <c r="L9" s="126">
+      <c r="L9" s="125">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="114">
+      <c r="M9" s="113">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="114" t="s">
+      <c r="N9" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="O9" s="106">
+      <c r="O9" s="105">
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="141" t="s">
+    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="140">
+      <c r="B10" s="139">
         <v>4104</v>
       </c>
-      <c r="C10" s="140">
+      <c r="C10" s="139">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="140">
+      <c r="D10" s="139">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="103">
         <f>+D10/E8</f>
         <v>4.6251588310038116E-2</v>
       </c>
-      <c r="F10" s="103">
+      <c r="F10" s="102">
         <f>+A8*E10</f>
         <v>18524.865606099109</v>
       </c>
-      <c r="G10" s="103">
+      <c r="G10" s="102">
         <f>+G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H10" s="102">
+      <c r="H10" s="101">
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="113">
         <v>60</v>
       </c>
-      <c r="L10" s="126">
+      <c r="L10" s="125">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="113">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="114" t="s">
+      <c r="N10" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="104">
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="141" t="s">
+    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="140">
+      <c r="B11" s="139">
         <v>7644</v>
       </c>
-      <c r="C11" s="140">
+      <c r="C11" s="139">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="140">
+      <c r="D11" s="139">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="E11" s="104">
+      <c r="E11" s="103">
         <f>+D11/E8</f>
         <v>8.2846251588310035E-2</v>
       </c>
-      <c r="F11" s="103">
+      <c r="F11" s="102">
         <f>+A8*E11</f>
         <v>33181.902129606096</v>
       </c>
-      <c r="G11" s="103">
+      <c r="G11" s="102">
         <f>G10</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H11" s="102">
+      <c r="H11" s="101">
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="114">
+      <c r="K11" s="113">
         <v>79</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="125">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="114">
+      <c r="M11" s="113">
         <v>0.03</v>
       </c>
-      <c r="N11" s="114" t="s">
+      <c r="N11" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="125">
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="141" t="s">
+    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="140">
+      <c r="B12" s="139">
         <v>6554</v>
       </c>
-      <c r="C12" s="140">
+      <c r="C12" s="139">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="140">
+      <c r="D12" s="139">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="103">
         <f>+D12/E8</f>
         <v>8.9453621346886919E-2</v>
       </c>
-      <c r="F12" s="103">
+      <c r="F12" s="102">
         <f>+A8*E12</f>
         <v>35828.311501905977</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H12" s="102">
+      <c r="H12" s="101">
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="114">
+      <c r="K12" s="113">
         <v>89</v>
       </c>
-      <c r="L12" s="126">
+      <c r="L12" s="125">
         <v>400</v>
       </c>
-      <c r="M12" s="114">
+      <c r="M12" s="113">
         <v>253</v>
       </c>
-      <c r="N12" s="114" t="s">
+      <c r="N12" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="O12" s="114">
+      <c r="O12" s="113">
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="141" t="s">
+    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="140">
+      <c r="B13" s="139">
         <v>7564</v>
       </c>
-      <c r="C13" s="140">
+      <c r="C13" s="139">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="140">
+      <c r="D13" s="139">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="E13" s="104">
+      <c r="E13" s="103">
         <f>+D13/E8</f>
         <v>0.10317662007623889</v>
       </c>
-      <c r="F13" s="103">
+      <c r="F13" s="102">
         <f>+A8*E13</f>
         <v>41324.700198221093</v>
       </c>
-      <c r="G13" s="103">
+      <c r="G13" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H13" s="102">
+      <c r="H13" s="101">
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="114">
+      <c r="K13" s="113">
         <v>140</v>
       </c>
-      <c r="L13" s="142">
+      <c r="L13" s="141">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="114">
+      <c r="M13" s="113">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="141" t="s">
+    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="140">
+      <c r="B14" s="139">
         <v>10119</v>
       </c>
-      <c r="C14" s="140">
+      <c r="C14" s="139">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="140">
+      <c r="D14" s="139">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="103">
         <f>+D14/E8</f>
         <v>0.10927573062261753</v>
       </c>
-      <c r="F14" s="103">
+      <c r="F14" s="102">
         <f>+A8*E14</f>
         <v>43767.539618805589</v>
       </c>
-      <c r="G14" s="103">
+      <c r="G14" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H14" s="102">
+      <c r="H14" s="101">
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="114">
+      <c r="K14" s="113">
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="141" t="s">
+    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="140" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="140">
+      <c r="B15" s="139">
         <v>8986</v>
       </c>
-      <c r="C15" s="140">
+      <c r="C15" s="139">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="140">
+      <c r="D15" s="139">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="E15" s="104">
+      <c r="E15" s="103">
         <f>+D15/E8</f>
         <v>4.1677255400254132E-2</v>
       </c>
-      <c r="F15" s="103">
+      <c r="F15" s="102">
         <f>+A8*E15</f>
         <v>16692.736040660737</v>
       </c>
-      <c r="G15" s="103">
+      <c r="G15" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H15" s="102">
+      <c r="H15" s="101">
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="114">
+      <c r="K15" s="113">
         <v>221</v>
       </c>
-      <c r="L15" s="114">
+      <c r="L15" s="113">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="141" t="s">
+    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="140">
+      <c r="B16" s="139">
         <v>7032</v>
       </c>
-      <c r="C16" s="140">
+      <c r="C16" s="139">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="140">
+      <c r="D16" s="139">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E16" s="104">
+      <c r="E16" s="103">
         <f>+D16/E8</f>
         <v>1.0165184243964421E-3</v>
       </c>
-      <c r="F16" s="103">
+      <c r="F16" s="102">
         <f>+A8*E16</f>
         <v>407.13990343074965</v>
       </c>
-      <c r="G16" s="103">
+      <c r="G16" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H16" s="102">
+      <c r="H16" s="101">
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="114">
+      <c r="K16" s="113">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="141" t="s">
+    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="140" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="140">
+      <c r="B17" s="139">
         <v>1623</v>
       </c>
-      <c r="C17" s="140">
+      <c r="C17" s="139">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="140">
+      <c r="D17" s="139">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="E17" s="104">
+      <c r="E17" s="103">
         <f>+D17/E8</f>
         <v>2.2871664548919948E-2</v>
       </c>
-      <c r="F17" s="103">
+      <c r="F17" s="102">
         <f>+A8*E17</f>
         <v>9160.6478271918677</v>
       </c>
-      <c r="G17" s="103">
+      <c r="G17" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H17" s="102">
+      <c r="H17" s="101">
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="114">
+      <c r="K17" s="113">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="141" t="s">
+    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="140" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="140">
+      <c r="B18" s="139">
         <v>3932</v>
       </c>
-      <c r="C18" s="140">
+      <c r="C18" s="139">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="140">
+      <c r="D18" s="139">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="E18" s="104">
+      <c r="E18" s="103">
         <f>+D18/E8</f>
         <v>4.5235069885641674E-2</v>
       </c>
-      <c r="F18" s="103">
+      <c r="F18" s="102">
         <f>+A8*E18</f>
         <v>18117.725702668358</v>
       </c>
-      <c r="G18" s="103">
+      <c r="G18" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H18" s="102">
+      <c r="H18" s="101">
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="114">
+      <c r="K18" s="113">
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="141" t="s">
+    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="140">
+      <c r="B19" s="139">
         <v>6887</v>
       </c>
-      <c r="C19" s="140">
+      <c r="C19" s="139">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="140">
+      <c r="D19" s="139">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="E19" s="104">
+      <c r="E19" s="103">
         <f>+D19/E8</f>
         <v>5.4383735705209657E-2</v>
       </c>
-      <c r="F19" s="103">
+      <c r="F19" s="102">
         <f>+A8*E19</f>
         <v>21781.98483354511</v>
       </c>
-      <c r="G19" s="103">
+      <c r="G19" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H19" s="102">
+      <c r="H19" s="101">
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="114">
+      <c r="K19" s="113">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="141" t="s">
+    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="140">
+      <c r="B20" s="139">
         <v>1884</v>
       </c>
-      <c r="C20" s="140">
+      <c r="C20" s="139">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="140">
+      <c r="D20" s="139">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="E20" s="104">
+      <c r="E20" s="103">
         <f>+D20/E8</f>
         <v>6.9123252858958067E-2</v>
       </c>
-      <c r="F20" s="103">
+      <c r="F20" s="102">
         <f>+A8*E20</f>
         <v>27685.513433290977</v>
       </c>
-      <c r="G20" s="103">
+      <c r="G20" s="102">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H20" s="102">
+      <c r="H20" s="101">
         <f t="shared" si="2"/>
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="139" t="s">
+    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="138" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="137">
+      <c r="B21" s="137"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="136">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="136"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="101">
+      <c r="E21" s="135"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="100">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="126">
+      <c r="J21" s="125">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="100">
+    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="99">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="135" t="s">
+      <c r="B22" s="134" t="s">
         <v>65</v>
       </c>
-      <c r="L22" s="134"/>
-    </row>
-    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="99">
+      <c r="L22" s="133"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="98">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="133" t="s">
+      <c r="B23" s="132" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="132"/>
-      <c r="J25" s="114">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="131"/>
+      <c r="J25" s="113">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="J26" s="114">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J26" s="113">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="114">
+    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J27" s="113">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="237" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B28" s="238" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="238"/>
-      <c r="D28" s="238"/>
-      <c r="E28" s="238"/>
-      <c r="F28" s="239"/>
-      <c r="J28" s="114">
+      <c r="C28" s="239"/>
+      <c r="D28" s="239"/>
+      <c r="E28" s="239"/>
+      <c r="F28" s="240"/>
+      <c r="J28" s="113">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B29" s="131" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B29" s="130" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="130" t="s">
+      <c r="C29" s="129" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="130" t="s">
+      <c r="D29" s="129" t="s">
         <v>135</v>
       </c>
-      <c r="E29" s="130" t="s">
+      <c r="E29" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="129" t="s">
+      <c r="F29" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="J29" s="114">
+      <c r="J29" s="113">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="125" t="s">
+    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B30" s="124" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="103">
+      <c r="C30" s="102">
         <v>4000</v>
       </c>
-      <c r="D30" s="103">
-        <v>0</v>
-      </c>
-      <c r="E30" s="123"/>
-      <c r="F30" s="102">
+      <c r="D30" s="102">
+        <v>0</v>
+      </c>
+      <c r="E30" s="122"/>
+      <c r="F30" s="101">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="128">
+      <c r="J30" s="127">
         <v>215</v>
       </c>
-      <c r="M30" s="114">
+      <c r="M30" s="113">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="125" t="s">
+    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B31" s="124" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="103">
+      <c r="C31" s="102">
         <v>4000</v>
       </c>
-      <c r="D31" s="103">
-        <v>0</v>
-      </c>
-      <c r="E31" s="123"/>
-      <c r="F31" s="102">
+      <c r="D31" s="102">
+        <v>0</v>
+      </c>
+      <c r="E31" s="122"/>
+      <c r="F31" s="101">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="114">
+      <c r="J31" s="113">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="125" t="s">
+    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B32" s="124" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="103">
+      <c r="C32" s="102">
         <v>4000</v>
       </c>
-      <c r="D32" s="103">
-        <v>0</v>
-      </c>
-      <c r="E32" s="123"/>
-      <c r="F32" s="102">
+      <c r="D32" s="102">
+        <v>0</v>
+      </c>
+      <c r="E32" s="122"/>
+      <c r="F32" s="101">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="114">
+      <c r="J32" s="113">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="125" t="s">
+    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B33" s="124" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="103">
+      <c r="C33" s="102">
         <v>4000</v>
       </c>
-      <c r="D33" s="103">
-        <v>0</v>
-      </c>
-      <c r="E33" s="123"/>
-      <c r="F33" s="102">
+      <c r="D33" s="102">
+        <v>0</v>
+      </c>
+      <c r="E33" s="122"/>
+      <c r="F33" s="101">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="114">
+      <c r="J33" s="113">
         <v>45</v>
       </c>
-      <c r="K33" s="127">
+      <c r="K33" s="126">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="125" t="s">
+    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B34" s="124" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="103">
+      <c r="C34" s="102">
         <v>4000</v>
       </c>
-      <c r="D34" s="103">
-        <v>0</v>
-      </c>
-      <c r="E34" s="123"/>
-      <c r="F34" s="102">
+      <c r="D34" s="102">
+        <v>0</v>
+      </c>
+      <c r="E34" s="122"/>
+      <c r="F34" s="101">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="114">
+      <c r="J34" s="113">
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="125" t="s">
+    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B35" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="103">
+      <c r="C35" s="102">
         <v>4000</v>
       </c>
-      <c r="D35" s="103">
-        <v>0</v>
-      </c>
-      <c r="E35" s="123"/>
-      <c r="F35" s="102">
+      <c r="D35" s="102">
+        <v>0</v>
+      </c>
+      <c r="E35" s="122"/>
+      <c r="F35" s="101">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="114">
+      <c r="J35" s="113">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="125" t="s">
+    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B36" s="124" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="103">
+      <c r="C36" s="102">
         <v>4000</v>
       </c>
-      <c r="D36" s="103">
-        <v>0</v>
-      </c>
-      <c r="E36" s="123"/>
-      <c r="F36" s="102">
+      <c r="D36" s="102">
+        <v>0</v>
+      </c>
+      <c r="E36" s="122"/>
+      <c r="F36" s="101">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="114">
+      <c r="J36" s="113">
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="125" t="s">
+    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B37" s="124" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="124">
+      <c r="C37" s="123">
         <v>4000</v>
       </c>
-      <c r="D37" s="103">
-        <v>0</v>
-      </c>
-      <c r="E37" s="123"/>
-      <c r="F37" s="102">
+      <c r="D37" s="102">
+        <v>0</v>
+      </c>
+      <c r="E37" s="122"/>
+      <c r="F37" s="101">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="125" t="s">
+    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B38" s="124" t="s">
         <v>124</v>
       </c>
-      <c r="C38" s="124">
+      <c r="C38" s="123">
         <v>4000</v>
       </c>
-      <c r="D38" s="124">
+      <c r="D38" s="123">
         <v>3500</v>
       </c>
-      <c r="E38" s="123" t="s">
+      <c r="E38" s="122" t="s">
         <v>123</v>
       </c>
-      <c r="F38" s="102">
+      <c r="F38" s="101">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="126">
+      <c r="M38" s="125">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="125" t="s">
+    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B39" s="124" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="124">
+      <c r="C39" s="123">
         <v>4000</v>
       </c>
-      <c r="D39" s="123"/>
-      <c r="E39" s="123"/>
-      <c r="F39" s="102">
+      <c r="D39" s="122"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="101">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="125" t="s">
+    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B40" s="124" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="124">
+      <c r="C40" s="123">
         <v>4000</v>
       </c>
-      <c r="D40" s="123"/>
-      <c r="E40" s="123"/>
-      <c r="F40" s="102">
+      <c r="D40" s="122"/>
+      <c r="E40" s="122"/>
+      <c r="F40" s="101">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="125" t="s">
+    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B41" s="124" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="124">
+      <c r="C41" s="123">
         <v>4000</v>
       </c>
-      <c r="D41" s="123"/>
-      <c r="E41" s="123"/>
-      <c r="F41" s="102">
+      <c r="D41" s="122"/>
+      <c r="E41" s="122"/>
+      <c r="F41" s="101">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="125" t="s">
+    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B42" s="124" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="124">
-        <v>0</v>
-      </c>
-      <c r="D42" s="123"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="102">
+      <c r="C42" s="123">
+        <v>0</v>
+      </c>
+      <c r="D42" s="122"/>
+      <c r="E42" s="122"/>
+      <c r="F42" s="101">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="125" t="s">
+    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B43" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="124">
-        <v>0</v>
-      </c>
-      <c r="D43" s="123"/>
-      <c r="E43" s="123"/>
-      <c r="F43" s="102">
+      <c r="C43" s="123">
+        <v>0</v>
+      </c>
+      <c r="D43" s="122"/>
+      <c r="E43" s="122"/>
+      <c r="F43" s="101">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="122" t="s">
+    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B44" s="121" t="s">
         <v>117</v>
       </c>
-      <c r="C44" s="121">
-        <v>0</v>
-      </c>
-      <c r="D44" s="120"/>
-      <c r="E44" s="120"/>
-      <c r="F44" s="119">
+      <c r="C44" s="120">
+        <v>0</v>
+      </c>
+      <c r="D44" s="119"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="118">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="122" t="s">
+    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B45" s="121" t="s">
         <v>116</v>
       </c>
-      <c r="C45" s="121">
-        <v>0</v>
-      </c>
-      <c r="D45" s="120"/>
-      <c r="E45" s="120"/>
-      <c r="F45" s="119">
+      <c r="C45" s="120">
+        <v>0</v>
+      </c>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="118">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="122" t="s">
+    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B46" s="121" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="121">
-        <v>0</v>
-      </c>
-      <c r="D46" s="120"/>
-      <c r="E46" s="120"/>
-      <c r="F46" s="119">
+      <c r="C46" s="120">
+        <v>0</v>
+      </c>
+      <c r="D46" s="119"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="118">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="118" t="s">
+    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="117">
+      <c r="C47" s="116">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="116"/>
-      <c r="E47" s="116"/>
-      <c r="F47" s="115">
+      <c r="D47" s="115"/>
+      <c r="E47" s="115"/>
+      <c r="F47" s="114">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>
